--- a/sources/jack2_step10.xlsx
+++ b/sources/jack2_step10.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD105"/>
+  <dimension ref="A1:AD107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4173,12 +4173,12 @@
     <row r="46">
       <c r="B46" t="inlineStr">
         <is>
-          <t>db+1,1,1,[1,1],2</t>
+          <t>db+1,1,1,2</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>db+1 ,1 ,1 ,[1 ,1] ,2</t>
+          <t>db+1 ,1 ,1 ,2</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>1 1 1 1 1 1</t>
+          <t>1 1 1 1</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4208,268 +4208,278 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>-6 -6 -6 -6 -11 -16</t>
+          <t>-6 -6 -11 -16</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-6 -6 -6 -6 -11 -16</t>
+          <t>-6 -6 -11 -16</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>+5 +5 +5 +5 0 KD</t>
+          <t>+5 +5 0 KD</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>+5 +5 +5 +5 0 KD</t>
+          <t>+5 +5 0 KD</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>+5 +5 +5 +5 0 KD</t>
+          <t>+5 +5 0 KD</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>+5 +5 +5 +5 0 KD</t>
+          <t>+5 +5 0 KD</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>12,15,15,15,15,40</t>
+          <t>12,15,15,40</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>82</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>12,15,15,15,15,40</t>
+          <t>12,15,15,40</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>lllllm</t>
+          <t>lllm</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>lllllm</t>
-        </is>
-      </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>RC</t>
+          <t>lllm</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>4cf7be1b-11d0-4c05-8424-e597df98603b</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>7cab04d2-5592-467a-bea7-99322350b7b3</t>
+          <t>dc5a29f5-7ecb-4a43-967e-7b5eadf20512</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="B47" t="inlineStr">
         <is>
-          <t>b,db,d,DF+1</t>
+          <t>db+1,1,1,1,2</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>b,db,d,DF+1</t>
+          <t>db+1 ,1 ,1 ,1 ,2</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Debugger</t>
+          <t>Machine Gun - Megaton Punch</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Debugger</t>
+          <t>Machine Gun - Megaton Punch</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1 1 1 1 1</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>-45</t>
+          <t>-6 -6 -6 -11 -16</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>-45</t>
+          <t>-6 -6 -6 -11 -16</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+5 +5 +5 0 KD</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+5 +5 +5 0 KD</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+5 +5 +5 0 KD</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+5 +5 +5 0 KD</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>12,15,15,15,40</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>97</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>12,15,15,15,40</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>llllm</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>RC</t>
+          <t>llllm</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>85158165-351f-41d2-8735-2ab0b63af148</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>2747e1e2-0cb3-4730-81ad-dc7a7427a2b6</t>
+          <t>b3cad2bc-95a3-4d7c-9abb-0335ed57fb7d</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="B48" t="inlineStr">
         <is>
-          <t>hcf</t>
+          <t>db+1,1,1,1,1,2</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>hcf</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>b,b+1</t>
+          <t>db+1 ,1 ,1 ,1 ,1 ,2</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Wind Up</t>
+          <t>Machine Gun - Megaton Punch</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Wind Up</t>
+          <t>Machine Gun - Megaton Punch</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1 1 1 1 1 1</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>-6 -6 -6 -6 -11 -16</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>-6 -6 -6 -6 -11 -16</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>+5 +5 +5 +5 0 KD</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>+5 +5 +5 +5 0 KD</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>+5 +5 +5 +5 0 KD</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>+5 +5 +5 +5 0 KD</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12,15,15,15,15,40</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12,15,15,15,15,40</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>lllllm</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>lllllm</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>c03fb65b-aaac-4006-8e2b-0a9f8c08fd8f</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>1a0aed99-b547-48d7-925a-8f99bbeb0917</t>
+          <t>3a6ce42c-3b05-4641-9152-428a8ed9fd0f</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="B49" t="inlineStr">
         <is>
-          <t>– 1</t>
+          <t>b,db,d,DF+1</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>hcf,1</t>
+          <t>b,db,d,DF+1</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Gigaton Punch</t>
+          <t>Debugger</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Wind Up – Gigaton Punch</t>
+          <t>Debugger</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4479,17 +4489,22 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>23</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>+21</t>
+          <t>-45</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>+21</t>
+          <t>-45</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -4514,69 +4529,69 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>-,20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>L</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>-m</t>
+          <t>L</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>RC</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2003590c-d918-44b9-ba39-ae204bd6ae62</t>
+          <t>85158165-351f-41d2-8735-2ab0b63af148</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>4b654016-9d3d-4588-aaf3-bcba06d600eb</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>c03fb65b-aaac-4006-8e2b-0a9f8c08fd8f</t>
+          <t>2747e1e2-0cb3-4730-81ad-dc7a7427a2b6</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="B50" t="inlineStr">
         <is>
-          <t>– DF+1</t>
+          <t>hcf</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>hcf,DF+1</t>
+          <t>hcf</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>b,b+1</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Debugger</t>
+          <t>Wind Up</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Wind Up – Debugger</t>
+          <t>Wind Up</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4584,768 +4599,728 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>-45</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>-45</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>-,25</t>
+          <t>-</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>-L</t>
-        </is>
-      </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>RC</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>bfcd8070-9fe9-4f68-b19e-bddec360b30a</t>
+          <t>c03fb65b-aaac-4006-8e2b-0a9f8c08fd8f</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>bc7743df-d62c-4baf-90d6-ca367a954aba</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>c03fb65b-aaac-4006-8e2b-0a9f8c08fd8f</t>
+          <t>1a0aed99-b547-48d7-925a-8f99bbeb0917</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="B51" t="inlineStr">
         <is>
-          <t>DF+1,2,1,2</t>
+          <t>– 1</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>DF+1 ,2 ,1 ,2</t>
+          <t>hcf,1</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Uppercut Rush</t>
+          <t>Gigaton Punch</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Uppercut Rush</t>
+          <t>Wind Up – Gigaton Punch</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>1 1 1 1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>14</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>-11 -7 -9 -2</t>
+          <t>+21</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>-11 -7 -9 -2</t>
+          <t>+21</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>KD +4 +2 +9</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>KD +4 +2 +9</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>KD +4 +2 +9</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>KD +4 +2 +9</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>10,15,10,15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>10,15,10,15</t>
+          <t>-,20</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>mmmm</t>
+          <t>m</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>mmmm</t>
+          <t>-m</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>JGc RC</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr">
-        <is>
-          <t>Juggles on the last hit if the first hit was a counter hit.</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>4f881878-519e-4f9f-bb13-ebe8511b7e9f</t>
+          <t>2003590c-d918-44b9-ba39-ae204bd6ae62</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>bf72dea8-4c41-4bb6-9420-9305240a53e3</t>
+          <t>4b654016-9d3d-4588-aaf3-bcba06d600eb</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>c03fb65b-aaac-4006-8e2b-0a9f8c08fd8f</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="B52" t="inlineStr">
         <is>
-          <t>Df+1,2,1</t>
+          <t>– DF+1</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Df+1 ,2 ,1</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>FC+DF+1,2,1</t>
+          <t>hcf,DF+1</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Quick Upper Rush</t>
+          <t>Debugger</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Quick Upper Rush</t>
+          <t>Wind Up – Debugger</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>1 1 1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>17</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>-6 -8 -2</t>
+          <t>-45</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>-6 -8 -2</t>
+          <t>-45</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>+5 +2 +9</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>+5 +2 +9</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>+5 +2 +9</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>+5 +2 +9</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>15,12,15</t>
+          <t>25</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>25</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>15,12,15</t>
+          <t>-,25</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>mmm</t>
+          <t>L</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>mmm</t>
+          <t>-L</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>JGc RC</t>
-        </is>
-      </c>
-      <c r="Y52" t="inlineStr">
-        <is>
-          <t>Juggles on the last hit if the first hit was a counter hit.</t>
+          <t>RC</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>7507a693-7948-45eb-a05e-3707d923e16d</t>
+          <t>bfcd8070-9fe9-4f68-b19e-bddec360b30a</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>b30faab6-54e4-4123-ab0b-5fb12faa3be2</t>
+          <t>bc7743df-d62c-4baf-90d6-ca367a954aba</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>c03fb65b-aaac-4006-8e2b-0a9f8c08fd8f</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="B53" t="inlineStr">
         <is>
-          <t>FC+df+1,2,1</t>
+          <t>DF+1,2,1,2</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>FC+df+1 ,2 ,1</t>
+          <t>DF+1 ,2 ,1 ,2</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Windmill</t>
+          <t>Uppercut Rush</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Windmill</t>
+          <t>Uppercut Rush</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>1 1 1</t>
+          <t>1 1 1 1</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>-22 -22 -2</t>
+          <t>-11 -7 -9 -2</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>-22 -22 -2</t>
+          <t>-11 -7 -9 -2</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>-12 -12 -12</t>
+          <t>KD +4 +2 +9</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>-12 -12 -12</t>
+          <t>KD +4 +2 +9</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>-12 -12 -12</t>
+          <t>KD +4 +2 +9</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>-12 -12 -12</t>
+          <t>KD +4 +2 +9</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>10,15,10</t>
+          <t>10,15,10,15</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>50</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>10,15,10</t>
+          <t>10,15,10,15</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>mmm</t>
+          <t>mmmm</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>mmm</t>
+          <t>mmmm</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>JGc RC</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>Juggles on the last hit if the first hit was a counter hit.</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>dbb96ec3-9f0f-4e57-b4ca-8de7e5046661</t>
+          <t>4f881878-519e-4f9f-bb13-ebe8511b7e9f</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>1c7f46c4-6ab3-4fdd-90e3-5f642409d3af</t>
+          <t>bf72dea8-4c41-4bb6-9420-9305240a53e3</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="B54" t="inlineStr">
         <is>
-          <t>– 1</t>
+          <t>Df+1,2,1</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>FC+df+1 ,2 ,1 ,1</t>
+          <t>Df+1 ,2 ,1</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>FC+DF+1,2,1</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>– Windmill Backhand</t>
+          <t>Quick Upper Rush</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Windmill – Windmill Backhand</t>
+          <t>Quick Upper Rush</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>1 1 1 1</t>
+          <t>1 1 1</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>17</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>+20</t>
+          <t>-6 -8 -2</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>-22 -22 -2 +20</t>
+          <t>-6 -8 -2</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+5 +2 +9</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>-12 -12 -12 KD</t>
+          <t>+5 +2 +9</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+5 +2 +9</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>-12 -12 -12 KD</t>
+          <t>+5 +2 +9</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>15,12,15</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>42</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>10,15,10,30</t>
+          <t>15,12,15</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>mmm</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>mmmh</t>
+          <t>mmm</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>CF GB</t>
+          <t>JGc RC</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>Juggles on the last hit if the first hit was a counter hit.</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>82838a4d-d558-42b7-ab73-e05d17ef4b08</t>
+          <t>7507a693-7948-45eb-a05e-3707d923e16d</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>e3e5f6b7-4929-4a52-8c31-e6806f1334ee</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>dbb96ec3-9f0f-4e57-b4ca-8de7e5046661</t>
+          <t>b30faab6-54e4-4123-ab0b-5fb12faa3be2</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="B55" t="inlineStr">
         <is>
-          <t>Df+1,2</t>
+          <t>FC+df+1,2,1</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Df+1 ,2</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>FC+DF+1,2</t>
+          <t>FC+df+1 ,2 ,1</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Medium Hammer Rush</t>
+          <t>Windmill</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Medium Hammer Rush</t>
+          <t>Windmill</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>1 1</t>
+          <t>1 1 1</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>-6 -8</t>
+          <t>-22 -22 -2</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>-6 -8</t>
+          <t>-22 -22 -2</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>+5 +2</t>
+          <t>-12 -12 -12</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>+5 +2</t>
+          <t>-12 -12 -12</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>+5 +2</t>
+          <t>-12 -12 -12</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>+5 +2</t>
+          <t>-12 -12 -12</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>15,12</t>
+          <t>10,15,10</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>35</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>15,12</t>
+          <t>10,15,10</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>mmm</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>RC</t>
+          <t>mmm</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>fb453abc-0836-42af-adee-dc8f713ceae0</t>
+          <t>dbb96ec3-9f0f-4e57-b4ca-8de7e5046661</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>53b77124-e72d-4f20-ae78-8225f04ac648</t>
+          <t>1c7f46c4-6ab3-4fdd-90e3-5f642409d3af</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="B56" t="inlineStr">
         <is>
-          <t>– d+1</t>
+          <t>– 1</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Df+1 ,2 ,d+1</t>
+          <t>FC+df+1 ,2 ,1 ,1</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>– Low Punch</t>
+          <t>– Windmill Backhand</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Medium Hammer Rush – Low Punch</t>
+          <t>Windmill – Windmill Backhand</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>1 1 1</t>
+          <t>1 1 1 1</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>+20</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>-6 -8 -17</t>
+          <t>-22 -22 -2 +20</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>+5 +2 -7</t>
+          <t>-12 -12 -12 KD</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>+5 +2 -7</t>
+          <t>-12 -12 -12 KD</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>30</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>30</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>15,12,8</t>
+          <t>10,15,10,30</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>h</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>mmL</t>
+          <t>mmmh</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>RC</t>
+          <t>CF GB</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>29dfa2dc-0160-4e71-b110-03e973136272</t>
+          <t>82838a4d-d558-42b7-ab73-e05d17ef4b08</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>be700e61-7fed-40b2-a16a-4b062cedd1c9</t>
+          <t>e3e5f6b7-4929-4a52-8c31-e6806f1334ee</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>fb453abc-0836-42af-adee-dc8f713ceae0</t>
+          <t>dbb96ec3-9f0f-4e57-b4ca-8de7e5046661</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="B57" t="inlineStr">
         <is>
-          <t>– df+1</t>
+          <t>Df+1,2</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Df+1 ,2 ,df+1</t>
+          <t>Df+1 ,2</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>FC+DF+1,2</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>– Mid Punch</t>
+          <t>Medium Hammer Rush</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Medium Hammer Rush – Mid Punch</t>
+          <t>Medium Hammer Rush</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>1 1 1</t>
+          <t>1 1</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>17</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -5355,57 +5330,57 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-6 -8</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>-6 -8 -1</t>
+          <t>-6 -8</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>+10</t>
+          <t>+5 +2</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>+5 +2 +10</t>
+          <t>+5 +2</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>+10</t>
+          <t>+5 +2</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>+5 +2 +10</t>
+          <t>+5 +2</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>15,12</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>27</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>15,12,15</t>
+          <t>15,12</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>mmm</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
@@ -5415,39 +5390,34 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>eb9bbfe4-68c3-4e58-baf7-821687138e91</t>
+          <t>fb453abc-0836-42af-adee-dc8f713ceae0</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>636b5aa8-46de-464e-81e9-d0bcfa43dc73</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>fb453abc-0836-42af-adee-dc8f713ceae0</t>
+          <t>53b77124-e72d-4f20-ae78-8225f04ac648</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="B58" t="inlineStr">
         <is>
-          <t>– f+1</t>
+          <t>– d+1</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Df+1 ,2 ,f+1</t>
+          <t>Df+1 ,2 ,d+1</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>– High Punch</t>
+          <t>– Low Punch</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Medium Hammer Rush – High Punch</t>
+          <t>Medium Hammer Rush – Low Punch</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -5472,57 +5442,62 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>+5 +2 -5</t>
+          <t>+5 +2 -7</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>+5 +2 -5</t>
+          <t>+5 +2 -7</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>15,12,12</t>
+          <t>15,12,8</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>L</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>mmh</t>
+          <t>mmL</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>RC</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>897a7dd1-1093-48ff-85f1-bebca88601ea</t>
+          <t>29dfa2dc-0160-4e71-b110-03e973136272</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>96ffff19-8555-4463-82fe-458f7c0c053b</t>
+          <t>be700e61-7fed-40b2-a16a-4b062cedd1c9</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
@@ -5534,92 +5509,87 @@
     <row r="59">
       <c r="B59" t="inlineStr">
         <is>
-          <t>FC+1,1,1,2</t>
+          <t>– df+1</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>FC+1 ,1 ,1 ,2</t>
+          <t>Df+1 ,2 ,df+1</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Hammer Rush</t>
+          <t>– Mid Punch</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Hammer Rush</t>
+          <t>Medium Hammer Rush – Mid Punch</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>1 1 1 1</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>19</t>
+          <t>1 1 1</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>-8 +1 -12 -8</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>-8 +1 -12 -8</t>
+          <t>-6 -8 -1</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>+2 +12 -1 +1</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>+2 +12 -1 +1</t>
+          <t>+5 +2 +10</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>+2 +12 -1 +1</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>+2 +12 -1 +1</t>
+          <t>+5 +2 +10</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>10,8,12,12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>15</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>10,8,12,12</t>
+          <t>15,12,15</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>LLmm</t>
+          <t>m</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>LLmm</t>
+          <t>mmm</t>
         </is>
       </c>
       <c r="X59" t="inlineStr">
@@ -5629,44 +5599,49 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>91a5d27a-8ea9-4505-8341-2bc54479b037</t>
+          <t>eb9bbfe4-68c3-4e58-baf7-821687138e91</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>87b157c8-bac6-4b55-a543-03b3e5c1c00f</t>
+          <t>636b5aa8-46de-464e-81e9-d0bcfa43dc73</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>fb453abc-0836-42af-adee-dc8f713ceae0</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="B60" t="inlineStr">
         <is>
-          <t>– d+1</t>
+          <t>– f+1</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>FC+1 ,1 ,1 ,2 ,d+1</t>
+          <t>Df+1 ,2 ,f+1</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>– Low Punch</t>
+          <t>– High Punch</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Hammer Rush – Low Punch</t>
+          <t>Medium Hammer Rush – High Punch</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>1 1 1 1 1</t>
+          <t>1 1 1</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -5676,99 +5651,99 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>-8 +1 -12 -8 -17</t>
+          <t>-6 -8 -17</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>+2 +12 -1 +1 -7</t>
+          <t>+5 +2 -5</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>+2 +12 -1 +1 -7</t>
+          <t>+5 +2 -5</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>10,8,12,12,8</t>
+          <t>15,12,12</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>h</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>LLmmL</t>
-        </is>
-      </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>RC</t>
+          <t>mmh</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>acb95787-cedc-4b5b-b8fb-50a3e72d4b5b</t>
+          <t>897a7dd1-1093-48ff-85f1-bebca88601ea</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>19e50734-0a3e-439a-bb45-d0541eae3da2</t>
+          <t>96ffff19-8555-4463-82fe-458f7c0c053b</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>91a5d27a-8ea9-4505-8341-2bc54479b037</t>
+          <t>fb453abc-0836-42af-adee-dc8f713ceae0</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="B61" t="inlineStr">
         <is>
-          <t>– df+1</t>
+          <t>FC+1,1,1,2</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>FC+1 ,1 ,1 ,2 ,df+1</t>
+          <t>FC+1 ,1 ,1 ,2</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>– Mid Punch</t>
+          <t>Hammer Rush</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Hammer Rush – Mid Punch</t>
+          <t>Hammer Rush</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>1 1 1 1 1</t>
+          <t>1 1 1 1</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>19</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -5778,57 +5753,57 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-8 +1 -12 -8</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>-8 +1 -12 -8 -1</t>
+          <t>-8 +1 -12 -8</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>+10</t>
+          <t>+2 +12 -1 +1</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>+2 +12 -1 +1 +10</t>
+          <t>+2 +12 -1 +1</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>+10</t>
+          <t>+2 +12 -1 +1</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>+2 +12 -1 +1 +10</t>
+          <t>+2 +12 -1 +1</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10,8,12,12</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>42</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>10,8,12,12,15</t>
+          <t>10,8,12,12</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>LLmm</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>LLmmm</t>
+          <t>LLmm</t>
         </is>
       </c>
       <c r="X61" t="inlineStr">
@@ -5838,39 +5813,34 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>756e1d64-081b-4d25-aaa0-fa5c3b7a738f</t>
+          <t>91a5d27a-8ea9-4505-8341-2bc54479b037</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>ecd60ebe-4c07-4ca2-a44b-3748905360dd</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>91a5d27a-8ea9-4505-8341-2bc54479b037</t>
+          <t>87b157c8-bac6-4b55-a543-03b3e5c1c00f</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="B62" t="inlineStr">
         <is>
-          <t>– f+1</t>
+          <t>– d+1</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>FC+1 ,1 ,1 ,2 ,f+1</t>
+          <t>FC+1 ,1 ,1 ,2 ,d+1</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>– High Punch</t>
+          <t>– Low Punch</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Hammer Rush – High Punch</t>
+          <t>Hammer Rush – Low Punch</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -5895,57 +5865,62 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>+2 +12 -1 +1 -5</t>
+          <t>+2 +12 -1 +1 -7</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>+2 +12 -1 +1 -5</t>
+          <t>+2 +12 -1 +1 -7</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>10,8,12,12,12</t>
+          <t>10,8,12,12,8</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>L</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>LLmmh</t>
+          <t>LLmmL</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>RC</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>ac1b3ebe-7028-47a0-be65-5eb121dab8bc</t>
+          <t>acb95787-cedc-4b5b-b8fb-50a3e72d4b5b</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>fe5b804b-6426-463e-b283-4eb22f9998b3</t>
+          <t>19e50734-0a3e-439a-bb45-d0541eae3da2</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
@@ -5957,92 +5932,87 @@
     <row r="63">
       <c r="B63" t="inlineStr">
         <is>
-          <t>FC+1,2</t>
+          <t>– df+1</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>FC+1 ,2</t>
+          <t>FC+1 ,1 ,1 ,2 ,df+1</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Low Punch - Megaton Punch</t>
+          <t>– Mid Punch</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Low Punch - Megaton Punch</t>
+          <t>Hammer Rush – Mid Punch</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>1 1</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
+          <t>1 1 1 1 1</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>-8 -14</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>-8 -14</t>
+          <t>-8 +1 -12 -8 -1</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>+2 KD</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>+2 KD</t>
+          <t>+2 +12 -1 +1 +10</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>+2 KD</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>+2 KD</t>
+          <t>+2 +12 -1 +1 +10</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>10,25</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>15</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>10,25</t>
+          <t>10,8,12,12,15</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>Lm</t>
+          <t>m</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>Lm</t>
+          <t>LLmmm</t>
         </is>
       </c>
       <c r="X63" t="inlineStr">
@@ -6052,151 +6022,146 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>06ab7954-5d39-49cc-91e3-02c54893dd53</t>
+          <t>756e1d64-081b-4d25-aaa0-fa5c3b7a738f</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>a769fb07-8a59-436e-a5fb-3acd34e8e01d</t>
+          <t>ecd60ebe-4c07-4ca2-a44b-3748905360dd</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>91a5d27a-8ea9-4505-8341-2bc54479b037</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="B64" t="inlineStr">
         <is>
-          <t>SS+1</t>
+          <t>– f+1</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>SS+1</t>
+          <t>FC+1 ,1 ,1 ,2 ,f+1</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Jack Hammer</t>
+          <t>– High Punch</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Jack Hammer</t>
+          <t>Hammer Rush – High Punch</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>32</t>
+          <t>1 1 1 1 1</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-17</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-8 +1 -12 -8 -17</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+2 +12 -1 +1 -5</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+2 +12 -1 +1 -5</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10,8,12,12,12</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>h</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="X64" t="inlineStr">
-        <is>
-          <t>BN GB</t>
-        </is>
-      </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>TRUE</t>
+          <t>LLmmh</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>41456c1a-f3a2-468f-b0ee-ee2032bb78c8</t>
+          <t>ac1b3ebe-7028-47a0-be65-5eb121dab8bc</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>de86a0e0-55fd-41e5-a239-a7685c39edbd</t>
+          <t>fe5b804b-6426-463e-b283-4eb22f9998b3</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>91a5d27a-8ea9-4505-8341-2bc54479b037</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="B65" t="inlineStr">
         <is>
-          <t>SS+1+2</t>
+          <t>FC+1,2</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>SS+1+2</t>
+          <t>FC+1 ,2</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Double Knuckle Swing</t>
+          <t>Low Punch - Megaton Punch</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Double Knuckle Swing</t>
+          <t>Low Punch - Megaton Punch</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1 1</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6211,308 +6176,313 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-8 -14</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-8 -14</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+2 KD</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+2 KD</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+2 KD</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+2 KD</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
+          <t>10,25</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="R65" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>10,25</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>Lm</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>Lm</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>RC</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>15c368e0-8f76-42a0-bbea-ef3cc510e19c</t>
+          <t>06ab7954-5d39-49cc-91e3-02c54893dd53</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2f8a7e04-7a60-430d-bc0a-6a55ed0d3427</t>
+          <t>a769fb07-8a59-436e-a5fb-3acd34e8e01d</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="B66" t="inlineStr">
         <is>
-          <t>1+2&lt;1+2</t>
+          <t>SS+1</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>1+2 &lt;1+2</t>
+          <t>SS+1</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Hammer Knuckle - Double Uppercut</t>
+          <t>Jack Hammer</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Hammer Knuckle - Double Uppercut</t>
+          <t>Jack Hammer</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>1 1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>-15 -20</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>-15 -20</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>KD KD</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>KD KD</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>KD KD</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>KD KD</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>21,22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>20</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>21,22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>m</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>m</t>
         </is>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>BN GB</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>54667fc1-c443-4001-a9d7-46c1d391bc4d</t>
+          <t>41456c1a-f3a2-468f-b0ee-ee2032bb78c8</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>36af744c-98c3-48c0-bea9-c96c61093c26</t>
+          <t>de86a0e0-55fd-41e5-a239-a7685c39edbd</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="B67" t="inlineStr">
         <is>
-          <t>WS+1+2&lt;1+2</t>
+          <t>SS+1+2</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>WS+1+2 &lt;1+2</t>
+          <t>SS+1+2</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Double Uppercut - Hammer Knuckle</t>
+          <t>Double Knuckle Swing</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Double Uppercut - Hammer Knuckle</t>
+          <t>Double Knuckle Swing</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>1 1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>-15 -16</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>-15 -16</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>KD KD</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>KD KD</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>KD KD</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>KD KD</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>21,17</t>
+          <t>35</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>35</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>21,17</t>
+          <t>35</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>h</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="X67" t="inlineStr">
-        <is>
-          <t>JG</t>
+          <t>h</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>14470b5f-e125-4262-857b-20fa6db24ee3</t>
+          <t>15c368e0-8f76-42a0-bbea-ef3cc510e19c</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>45985eea-a458-447f-9b9d-941ed088446a</t>
+          <t>2f8a7e04-7a60-430d-bc0a-6a55ed0d3427</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="B68" t="inlineStr">
         <is>
-          <t>f+1+2</t>
+          <t>1+2&lt;1+2</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>f+1+2</t>
+          <t>1+2 &lt;1+2</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Arm Scissors</t>
+          <t>Hammer Knuckle - Double Uppercut</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Arm Scissors</t>
+          <t>Hammer Knuckle - Double Uppercut</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1 1</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6527,94 +6497,94 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-15 -20</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-15 -20</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>KD KD</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>KD KD</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>KD KD</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>KD KD</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>21,22</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>43</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>21,22</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>JG</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>fab4def4-7c2d-4882-ac15-2c257a91fc81</t>
+          <t>54667fc1-c443-4001-a9d7-46c1d391bc4d</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>f51b4cde-994c-422f-b3e6-3e932f7d87ff</t>
+          <t>36af744c-98c3-48c0-bea9-c96c61093c26</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="B69" t="inlineStr">
         <is>
-          <t>– 1+2</t>
+          <t>WS+1+2&lt;1+2</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>f+1+2 ,1+2</t>
+          <t>WS+1+2 &lt;1+2</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>– Cross Cut Saw</t>
+          <t>Double Uppercut - Hammer Knuckle</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Arm Scissors – Cross Cut Saw</t>
+          <t>Double Uppercut - Hammer Knuckle</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -6622,24 +6592,29 @@
           <t>1 1</t>
         </is>
       </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>-14</t>
+          <t>-15 -16</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>-10 -14</t>
+          <t>-15 -16</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>KD KD</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -6649,7 +6624,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>KD KD</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -6659,74 +6634,74 @@
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>21,17</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>38</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>17,15</t>
+          <t>21,17</t>
         </is>
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>l</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>RC</t>
+          <t>JG</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>acab70ca-8813-48c6-907e-58ba82b57685</t>
+          <t>14470b5f-e125-4262-857b-20fa6db24ee3</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>e7af4cd0-902b-4b89-9c43-ea9365bec42c</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>fab4def4-7c2d-4882-ac15-2c257a91fc81</t>
+          <t>45985eea-a458-447f-9b9d-941ed088446a</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="B70" t="inlineStr">
         <is>
-          <t>– ~df+2</t>
+          <t>f+1+2</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>f+1+2 ~df+2</t>
+          <t>f+1+2</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>– Megaton Punch</t>
+          <t>Arm Scissors</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Arm Scissors – Megaton Punch</t>
+          <t>Arm Scissors</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>1 1</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>17</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -6736,12 +6711,12 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>-19</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>-10 -19</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -6751,7 +6726,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>KD KD</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -6761,22 +6736,22 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>KD KD</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>17</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>17,25</t>
+          <t>17</t>
         </is>
       </c>
       <c r="T70" t="inlineStr">
@@ -6786,74 +6761,64 @@
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>m</t>
         </is>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>RC</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>773af138-28f0-48ff-9b0e-97e83d2d8d3f</t>
+          <t>fab4def4-7c2d-4882-ac15-2c257a91fc81</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>b671f9fe-a460-4157-8300-00379e99322d</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>fab4def4-7c2d-4882-ac15-2c257a91fc81</t>
+          <t>f51b4cde-994c-422f-b3e6-3e932f7d87ff</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="B71" t="inlineStr">
         <is>
-          <t>d+1+2</t>
+          <t>– 1+2</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>d+1+2</t>
+          <t>f+1+2 ,1+2</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Bravo Knuckle</t>
+          <t>– Cross Cut Saw</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Bravo Knuckle</t>
+          <t>Arm Scissors – Cross Cut Saw</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>1 1</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>-23</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>-23</t>
+          <t>-10 -14</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -6863,104 +6828,94 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
+          <t>KD KD</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O71" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>KD KD</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>15</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>17,15</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>l</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>JG GB</t>
-        </is>
-      </c>
-      <c r="Y71" t="inlineStr">
-        <is>
-          <t>When tagging in Bryan Fury hit 2 to grab the opponent in mid air and do a Fisherman's Slam. Total damage is 21,21.</t>
-        </is>
-      </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>TRUE</t>
+          <t>RC</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>f79bf7d8-dcd1-4a58-883f-38e113a7b9e1</t>
+          <t>acab70ca-8813-48c6-907e-58ba82b57685</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2ecc5ad9-b4ca-485a-884a-0301a91b3509</t>
+          <t>e7af4cd0-902b-4b89-9c43-ea9365bec42c</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>fab4def4-7c2d-4882-ac15-2c257a91fc81</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="B72" t="inlineStr">
         <is>
-          <t>FC+1+2</t>
+          <t>– ~df+2</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>FC+1+2</t>
+          <t>f+1+2 ~df+2</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Cross Cut Saw</t>
+          <t>– Megaton Punch</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Cross Cut Saw</t>
+          <t>Arm Scissors – Megaton Punch</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>21</t>
+          <t>1 1</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -6970,7 +6925,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>-19</t>
+          <t>-10 -19</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -6980,42 +6935,42 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
+          <t>KD KD</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O72" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>KD KD</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>25</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>25</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17,25</t>
         </is>
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>l</t>
+          <t>m</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>l</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="X72" t="inlineStr">
@@ -7025,477 +6980,487 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>23e71f4e-0ab8-4ddc-89c1-4b2fe81234cc</t>
+          <t>773af138-28f0-48ff-9b0e-97e83d2d8d3f</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>52606470-ef56-4c68-a311-9fe12c9a5f23</t>
+          <t>b671f9fe-a460-4157-8300-00379e99322d</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>fab4def4-7c2d-4882-ac15-2c257a91fc81</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="B73" t="inlineStr">
         <is>
-          <t>Df+2,1,2</t>
+          <t>d+1+2</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Df+2 ,1 ,2</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>FC+DF+2,1,2</t>
+          <t>d+1+2</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Quick Uppercut Rush</t>
+          <t>Bravo Knuckle</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Quick Uppercut Rush</t>
+          <t>Bravo Knuckle</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>1 1 1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>-9 -2 -9</t>
+          <t>-23</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>-9 -2 -9</t>
+          <t>-23</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>-2 +10 +2</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>-2 +10 +2</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>-2 +10 +2</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>-2 +10 +2</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>15,10,15</t>
+          <t>45</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>45</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>15,10,15</t>
+          <t>45</t>
         </is>
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>mmm</t>
+          <t>m</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>mmm</t>
+          <t>m</t>
         </is>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>JGc RC</t>
+          <t>JG GB</t>
         </is>
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>Juggles on the last hit if the first hit was a counter hit.</t>
+          <t>When tagging in Bryan Fury hit 2 to grab the opponent in mid air and do a Fisherman's Slam. Total damage is 21,21.</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>38964142-4e38-457c-9a6d-9ef0fcf12cd4</t>
+          <t>f79bf7d8-dcd1-4a58-883f-38e113a7b9e1</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>8efe400a-6435-45e4-92f5-b9e1d4fd9595</t>
+          <t>2ecc5ad9-b4ca-485a-884a-0301a91b3509</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="B74" t="inlineStr">
         <is>
-          <t>DF+2,1,2,1</t>
+          <t>FC+1+2</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>DF+2 ,1 ,2 ,1</t>
+          <t>FC+1+2</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Hammer Uppercut Rush</t>
+          <t>Cross Cut Saw</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Hammer Uppercut Rush</t>
+          <t>Cross Cut Saw</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>1 1 1 1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>-11 -6 -9 -1</t>
+          <t>-19</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>-11 -6 -9 -1</t>
+          <t>-19</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>KD +5 +3 +10</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>KD +5 +3 +10</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>KD +5 +3 +10</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>KD +5 +3 +10</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>10,15,12,15</t>
+          <t>21</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>21</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>10,15,12,15</t>
+          <t>21</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>mmmm</t>
+          <t>l</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>mmmm</t>
+          <t>l</t>
         </is>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>JG RC</t>
+          <t>RC</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>f62fd939-223c-47b4-982b-aecff23cfca4</t>
+          <t>23e71f4e-0ab8-4ddc-89c1-4b2fe81234cc</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>e85a400e-73a4-495b-917a-82244da3681f</t>
+          <t>52606470-ef56-4c68-a311-9fe12c9a5f23</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="B75" t="inlineStr">
         <is>
-          <t>f,f+2</t>
+          <t>Df+2,1,2</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>f,f+2</t>
+          <t>Df+2 ,1 ,2</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>FC+DF+2,1,2</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Atomic Hook</t>
+          <t>Quick Uppercut Rush</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Atomic Hook</t>
+          <t>Quick Uppercut Rush</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1 1 1</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-9 -2 -9</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-9 -2 -9</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-2 +10 +2</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-2 +10 +2</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-2 +10 +2</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-2 +10 +2</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>15,10,15</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>40</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>15,10,15</t>
         </is>
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>mmm</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>mmm</t>
+        </is>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>JGc RC</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>Juggles on the last hit if the first hit was a counter hit.</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>e3ef4e95-cdea-4525-83df-74474e814b2a</t>
+          <t>38964142-4e38-457c-9a6d-9ef0fcf12cd4</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>e14fe285-946c-414b-88e4-d7e2f3af2745</t>
+          <t>8efe400a-6435-45e4-92f5-b9e1d4fd9595</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="B76" t="inlineStr">
         <is>
-          <t>2,1,2</t>
+          <t>DF+2,1,2,1</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2 ,1 ,2</t>
+          <t>DF+2 ,1 ,2 ,1</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Punch - Elbow - Uppercut</t>
+          <t>Hammer Uppercut Rush</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Punch - Elbow - Uppercut</t>
+          <t>Hammer Uppercut Rush</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>1 1 1</t>
+          <t>1 1 1 1</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>0 0 -15</t>
+          <t>-11 -6 -9 -1</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>0 0 -15</t>
+          <t>-11 -6 -9 -1</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>+7 +2 KD</t>
+          <t>KD +5 +3 +10</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>+7 +2 KD</t>
+          <t>KD +5 +3 +10</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>+7 +2 KD</t>
+          <t>KD +5 +3 +10</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>+7 +2 KD</t>
+          <t>KD +5 +3 +10</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>12,15,20</t>
+          <t>10,15,12,15</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>52</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>12,15,20</t>
+          <t>10,15,12,15</t>
         </is>
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>mmmm</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>mmmm</t>
         </is>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>JG</t>
-        </is>
-      </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>TRUE</t>
+          <t>JG RC</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>b51b9f18-a0d7-4234-b6c4-e0db8e729094</t>
+          <t>f62fd939-223c-47b4-982b-aecff23cfca4</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>06e4e99f-b024-4491-a080-43e24bdee8bc</t>
+          <t>e85a400e-73a4-495b-917a-82244da3681f</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="B77" t="inlineStr">
         <is>
-          <t>Df+2</t>
+          <t>f,f+2</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Df+2</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>FC+df+2</t>
+          <t>f,f+2</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Short Hammer Rush</t>
+          <t>Atomic Hook</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Short Hammer Rush</t>
+          <t>Atomic Hook</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -7505,216 +7470,226 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>-13</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>-13</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>27</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>27</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>27</t>
         </is>
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>h</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="X77" t="inlineStr">
-        <is>
-          <t>RC</t>
+          <t>h</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>0e04bfed-33f9-495b-b9db-252a47602a7d</t>
+          <t>e3ef4e95-cdea-4525-83df-74474e814b2a</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>d79c3cf7-3a6f-4c0a-b31a-e35de47e6878</t>
+          <t>e14fe285-946c-414b-88e4-d7e2f3af2745</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="B78" t="inlineStr">
         <is>
-          <t>– d+1</t>
+          <t>2,1,2</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Df+2 ,d+1</t>
+          <t>2 ,1 ,2</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>– Low Punch</t>
+          <t>Punch - Elbow - Uppercut</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Short Hammer Rush – Low Punch</t>
+          <t>Punch - Elbow - Uppercut</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>1 1</t>
+          <t>1 1 1</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>0 0 -15</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>-13 -17</t>
+          <t>0 0 -15</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>+7 +2 KD</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>-2 -7</t>
+          <t>+7 +2 KD</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>+7 +2 KD</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>-2 -7</t>
+          <t>+7 +2 KD</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12,15,20</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>47</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>10,8</t>
+          <t>12,15,20</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>mL</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>RC</t>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>82744639-21bd-464e-acb0-fb430a833b71</t>
+          <t>b51b9f18-a0d7-4234-b6c4-e0db8e729094</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>da44dd7b-4cdb-4823-a817-06318a68273c</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>0e04bfed-33f9-495b-b9db-252a47602a7d</t>
+          <t>06e4e99f-b024-4491-a080-43e24bdee8bc</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="B79" t="inlineStr">
         <is>
-          <t>– df+1</t>
+          <t>Df+2</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Df+2 ,df+1</t>
+          <t>Df+2</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>FC+df+2</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>– Mid Punch</t>
+          <t>Short Hammer Rush</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Short Hammer Rush – Mid Punch</t>
+          <t>Short Hammer Rush</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>1 1</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>18</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -7724,47 +7699,47 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>-13 -1</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>+10</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>-2 +10</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>+10</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>-2 +10</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>10,15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="T79" t="inlineStr">
@@ -7774,7 +7749,7 @@
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>m</t>
         </is>
       </c>
       <c r="X79" t="inlineStr">
@@ -7784,39 +7759,34 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>9cba188e-9985-4f96-83e4-7db5474781d2</t>
+          <t>0e04bfed-33f9-495b-b9db-252a47602a7d</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>51f0fb87-39b1-45cd-ab41-c081312a5d9b</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>0e04bfed-33f9-495b-b9db-252a47602a7d</t>
+          <t>d79c3cf7-3a6f-4c0a-b31a-e35de47e6878</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="B80" t="inlineStr">
         <is>
-          <t>– f+1</t>
+          <t>– d+1</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Df+2 ,f+1</t>
+          <t>Df+2 ,d+1</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>– High Punch</t>
+          <t>– Low Punch</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Short Hammer Rush – High Punch</t>
+          <t>Short Hammer Rush – Low Punch</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -7841,57 +7811,62 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>-2 -5</t>
+          <t>-2 -7</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>-2 -5</t>
+          <t>-2 -7</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>10,12</t>
+          <t>10,8</t>
         </is>
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>L</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>mh</t>
+          <t>mL</t>
+        </is>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>RC</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>9dd1c03f-e1e1-4e41-b91a-88df8054ec5c</t>
+          <t>82744639-21bd-464e-acb0-fb430a833b71</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>529ea903-bd1d-4081-ab74-eb6b82eaab94</t>
+          <t>da44dd7b-4cdb-4823-a817-06318a68273c</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
@@ -7903,82 +7878,77 @@
     <row r="81">
       <c r="B81" t="inlineStr">
         <is>
-          <t>b,db,d,DF+2</t>
+          <t>– df+1</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>b,db,d,DF+2</t>
+          <t>Df+2 ,df+1</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Megaton Punch</t>
+          <t>– Mid Punch</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Megaton Punch</t>
+          <t>Short Hammer Rush – Mid Punch</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>21</t>
+          <t>1 1</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>-13 -1</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-2 +10</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-2 +10</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>15</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>10,15</t>
         </is>
       </c>
       <c r="T81" t="inlineStr">
@@ -7988,7 +7958,7 @@
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="X81" t="inlineStr">
@@ -7998,141 +7968,141 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>56b1623c-ef98-42a3-be49-2ebc46462a0f</t>
+          <t>9cba188e-9985-4f96-83e4-7db5474781d2</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>e818b2a1-12e3-409b-8e48-4b059aaa76c0</t>
+          <t>51f0fb87-39b1-45cd-ab41-c081312a5d9b</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>0e04bfed-33f9-495b-b9db-252a47602a7d</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="B82" t="inlineStr">
         <is>
-          <t>f,f+3</t>
+          <t>– f+1</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>f,f+3</t>
+          <t>Df+2 ,f+1</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Granite Stomp</t>
+          <t>– High Punch</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Granite Stomp</t>
+          <t>Short Hammer Rush – High Punch</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>25</t>
+          <t>1 1</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>-17</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>-13 -17</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-2 -5</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-2 -5</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>12</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>10,12</t>
         </is>
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>h</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>mh</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>ee6c0589-29fe-439a-8f69-242d8e6811f6</t>
+          <t>9dd1c03f-e1e1-4e41-b91a-88df8054ec5c</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>879d1a1f-95b2-4081-aa4b-dc74da0c13c6</t>
+          <t>529ea903-bd1d-4081-ab74-eb6b82eaab94</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>0e04bfed-33f9-495b-b9db-252a47602a7d</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="B83" t="inlineStr">
         <is>
-          <t>f+3+4</t>
+          <t>b,db,d,DF+2</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>f+3+4</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>FC+df+3+4</t>
+          <t>b,db,d,DF+2</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Giga Shoulder Ram</t>
+          <t>Megaton Punch</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Giga Shoulder Ram</t>
+          <t>Megaton Punch</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -8152,12 +8122,12 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-17</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-17</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -8182,17 +8152,17 @@
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>33</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>33</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>33</t>
         </is>
       </c>
       <c r="T83" t="inlineStr">
@@ -8205,138 +8175,148 @@
           <t>m</t>
         </is>
       </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>RC</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>20d7633a-2326-4494-84f9-0a235f1c2fe8</t>
+          <t>56b1623c-ef98-42a3-be49-2ebc46462a0f</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>b0da65f9-bf50-406e-8de8-7db02d0abb2c</t>
+          <t>e818b2a1-12e3-409b-8e48-4b059aaa76c0</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="B84" t="inlineStr">
         <is>
-          <t>DB+3,4,3,4,3,4</t>
+          <t>f,f+3</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>DB+3 ,4 ,3 ,4 ,3 ,4</t>
+          <t>f,f+3</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Cossack Kicks</t>
+          <t>Granite Stomp</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Cossack Kicks</t>
+          <t>Granite Stomp</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>1 1 1 1 1 1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>-20 -22 -20 -22...</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>-20 -22 -20 -22...</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>-9 -11 -9 -11...</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>-9 -11 -9 -11...</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>-9 -11 -9 -11...</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>-9 -11 -9 -11...</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>18,12,10,12,12,12</t>
+          <t>22</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>22</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>18,12,10,12,12,12</t>
+          <t>22</t>
         </is>
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>LLLLLL</t>
+          <t>M</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>LLLLLL</t>
+          <t>M</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>674f6841-5fbb-4b15-865f-9ab351c1a0f0</t>
+          <t>ee6c0589-29fe-439a-8f69-242d8e6811f6</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>4c477a6b-86e6-43f8-911d-93481004b0b5</t>
+          <t>879d1a1f-95b2-4081-aa4b-dc74da0c13c6</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="B85" t="inlineStr">
         <is>
-          <t>uf+3+4</t>
+          <t>f+3+4</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>uf+3+4</t>
+          <t>f+3+4</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>FC+df+3+4</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Hip Press</t>
+          <t>Giga Shoulder Ram</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Hip Press</t>
+          <t>Giga Shoulder Ram</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -8346,1398 +8326,1498 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>-40</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>-40</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>-40</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>-40</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>m</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="Y85" t="inlineStr">
-        <is>
-          <t>If the Hip Press Misses the opponent, Jack-2 can chain into Sit Down extentions.</t>
+          <t>m</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>3be14565-e783-4db3-9168-bf98e290f21d</t>
+          <t>20d7633a-2326-4494-84f9-0a235f1c2fe8</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>ce4da910-2232-4be6-a896-136d900764e1</t>
+          <t>b0da65f9-bf50-406e-8de8-7db02d0abb2c</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="B86" t="inlineStr">
         <is>
+          <t>DB+3,4,3,4,3,4</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>DB+3 ,4 ,3 ,4 ,3 ,4</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Cossack Kicks</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Cossack Kicks</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>1 1 1 1 1 1</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>-20 -22 -20 -22...</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>-20 -22 -20 -22...</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>-9 -11 -9 -11...</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>-9 -11 -9 -11...</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>-9 -11 -9 -11...</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>-9 -11 -9 -11...</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>18,12,10,12,12,12</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>18,12,10,12,12,12</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>LLLLLL</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>LLLLLL</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>674f6841-5fbb-4b15-865f-9ab351c1a0f0</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>4c477a6b-86e6-43f8-911d-93481004b0b5</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>uf+3+4</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>uf+3+4</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Hip Press</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Hip Press</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>-40</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>-40</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>-40</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>-40</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>If the Hip Press Misses the opponent, Jack-2 can chain into Sit Down extentions.</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>3be14565-e783-4db3-9168-bf98e290f21d</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>ce4da910-2232-4be6-a896-136d900764e1</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" t="inlineStr">
+        <is>
           <t>3+4</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
+      <c r="C88" t="inlineStr">
         <is>
           <t>3+4</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="E88" t="inlineStr">
         <is>
           <t>Sit Down</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
+      <c r="F88" t="inlineStr">
         <is>
           <t>Sit Down</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
+      <c r="H88" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q86" t="inlineStr">
+      <c r="Q88" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R86" t="inlineStr">
+      <c r="R88" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S86" t="inlineStr">
+      <c r="S88" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="T86" t="inlineStr">
+      <c r="T88" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="U86" t="inlineStr">
+      <c r="U88" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AA86" t="inlineStr">
+      <c r="AA88" t="inlineStr">
         <is>
           <t>3f1586e3-7d70-40ce-a201-943ab9917e0a</t>
         </is>
       </c>
-      <c r="AB86" t="inlineStr">
+      <c r="AB88" t="inlineStr">
         <is>
           <t>8ff726df-3bc4-4645-98be-c2fad557ee7d</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="B87">
+    <row r="89">
+      <c r="B89">
         <f>~3+4</f>
         <v/>
       </c>
-      <c r="C87">
+      <c r="C89">
         <f>~3+4</f>
         <v/>
       </c>
-      <c r="E87" t="inlineStr">
+      <c r="E89" t="inlineStr">
         <is>
           <t>– Hop Hip Press</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
+      <c r="F89" t="inlineStr">
         <is>
           <t>– Hop Hip Press</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
+      <c r="H89" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
+      <c r="I89" t="inlineStr">
         <is>
           <t>62</t>
         </is>
       </c>
-      <c r="J87" t="inlineStr">
+      <c r="J89" t="inlineStr">
         <is>
           <t>62</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr">
+      <c r="K89" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="L87" t="inlineStr">
+      <c r="L89" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="M87" t="inlineStr">
+      <c r="M89" t="inlineStr">
         <is>
           <t>-34</t>
         </is>
       </c>
-      <c r="N87" t="inlineStr">
+      <c r="N89" t="inlineStr">
         <is>
           <t>-34</t>
         </is>
       </c>
-      <c r="O87" t="inlineStr">
+      <c r="O89" t="inlineStr">
         <is>
           <t>-34</t>
         </is>
       </c>
-      <c r="P87" t="inlineStr">
+      <c r="P89" t="inlineStr">
         <is>
           <t>-34</t>
         </is>
       </c>
-      <c r="Q87" t="inlineStr">
+      <c r="Q89" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="R87" t="inlineStr">
+      <c r="R89" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="S87" t="inlineStr">
+      <c r="S89" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="T87" t="inlineStr">
+      <c r="T89" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="U87" t="inlineStr">
+      <c r="U89" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="Y87" t="inlineStr">
+      <c r="Y89" t="inlineStr">
         <is>
           <t>If the Hip Press Misses the opponent, Jack-2 can chain into Sit Down extentions.</t>
         </is>
       </c>
-      <c r="AA87" t="inlineStr">
+      <c r="AA89" t="inlineStr">
         <is>
           <t>421087d9-77e4-4344-95d3-0ffee0325022</t>
         </is>
       </c>
-      <c r="AB87" t="inlineStr">
+      <c r="AB89" t="inlineStr">
         <is>
           <t>1f37a24d-750f-4851-a2b5-a6b9a1b4ed26</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="B88" t="inlineStr">
+    <row r="90">
+      <c r="B90" t="inlineStr">
         <is>
           <t>– B</t>
         </is>
       </c>
-      <c r="C88">
+      <c r="C90">
         <f>~3+4,B</f>
         <v/>
       </c>
-      <c r="E88" t="inlineStr">
+      <c r="E90" t="inlineStr">
         <is>
           <t>– Roll Back</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
+      <c r="F90" t="inlineStr">
         <is>
           <t>– Hop Hip Press – Roll Back</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
+      <c r="H90" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J88" t="inlineStr">
+      <c r="J90" t="inlineStr">
         <is>
           <t>62</t>
         </is>
       </c>
-      <c r="L88" t="inlineStr">
+      <c r="L90" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="N88" t="inlineStr">
+      <c r="N90" t="inlineStr">
         <is>
           <t>-34</t>
         </is>
       </c>
-      <c r="P88" t="inlineStr">
+      <c r="P90" t="inlineStr">
         <is>
           <t>-34</t>
         </is>
       </c>
-      <c r="Q88" t="inlineStr">
+      <c r="Q90" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R88" t="inlineStr">
+      <c r="R90" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S88" t="inlineStr">
+      <c r="S90" t="inlineStr">
         <is>
           <t>35,-</t>
         </is>
       </c>
-      <c r="T88" t="inlineStr">
+      <c r="T90" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="U88" t="inlineStr">
+      <c r="U90" t="inlineStr">
         <is>
           <t>M-</t>
         </is>
       </c>
-      <c r="AA88" t="inlineStr">
+      <c r="AA90" t="inlineStr">
         <is>
           <t>a96a391b-b0cf-493d-a205-6511f1e34903</t>
         </is>
       </c>
-      <c r="AB88" t="inlineStr">
+      <c r="AB90" t="inlineStr">
         <is>
           <t>4f15e677-cb84-4d03-b6d8-82c26255c1d9</t>
         </is>
       </c>
-      <c r="AC88" t="inlineStr">
+      <c r="AC90" t="inlineStr">
         <is>
           <t>421087d9-77e4-4344-95d3-0ffee0325022</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="B89" t="inlineStr">
+    <row r="91">
+      <c r="B91" t="inlineStr">
         <is>
           <t>– F</t>
         </is>
       </c>
-      <c r="C89">
+      <c r="C91">
         <f>~3+4,F</f>
         <v/>
       </c>
-      <c r="E89" t="inlineStr">
+      <c r="E91" t="inlineStr">
         <is>
           <t>– Roll Forward</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
+      <c r="F91" t="inlineStr">
         <is>
           <t>– Hop Hip Press – Roll Forward</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
+      <c r="H91" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J89" t="inlineStr">
+      <c r="J91" t="inlineStr">
         <is>
           <t>62</t>
         </is>
       </c>
-      <c r="L89" t="inlineStr">
+      <c r="L91" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="N89" t="inlineStr">
+      <c r="N91" t="inlineStr">
         <is>
           <t>-34</t>
         </is>
       </c>
-      <c r="P89" t="inlineStr">
+      <c r="P91" t="inlineStr">
         <is>
           <t>-34</t>
         </is>
       </c>
-      <c r="Q89" t="inlineStr">
+      <c r="Q91" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R89" t="inlineStr">
+      <c r="R91" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S89" t="inlineStr">
+      <c r="S91" t="inlineStr">
         <is>
           <t>35,-</t>
         </is>
       </c>
-      <c r="T89" t="inlineStr">
+      <c r="T91" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="U89" t="inlineStr">
+      <c r="U91" t="inlineStr">
         <is>
           <t>M-</t>
         </is>
       </c>
-      <c r="AA89" t="inlineStr">
+      <c r="AA91" t="inlineStr">
         <is>
           <t>df8e44d6-d84c-4ee6-8117-15cb0b65ceb6</t>
         </is>
       </c>
-      <c r="AB89" t="inlineStr">
+      <c r="AB91" t="inlineStr">
         <is>
           <t>0680a704-d8c9-47e5-91a9-98babe1c15af</t>
         </is>
       </c>
-      <c r="AC89" t="inlineStr">
+      <c r="AC91" t="inlineStr">
         <is>
           <t>421087d9-77e4-4344-95d3-0ffee0325022</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="B90" t="inlineStr">
+    <row r="92">
+      <c r="B92" t="inlineStr">
         <is>
           <t>– 1,2,1,2</t>
         </is>
       </c>
-      <c r="C90">
+      <c r="C92">
         <f>~3+4 ,1 ,2 ,1 ,2</f>
         <v/>
       </c>
-      <c r="E90" t="inlineStr">
+      <c r="E92" t="inlineStr">
         <is>
           <t>– Sitting Punches</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
+      <c r="F92" t="inlineStr">
         <is>
           <t>– Hop Hip Press – Sitting Punches</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
+      <c r="H92" t="inlineStr">
         <is>
           <t>1 1 1 1 1</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
+      <c r="I92" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="J90" t="inlineStr">
+      <c r="J92" t="inlineStr">
         <is>
           <t>62</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr">
+      <c r="K92" t="inlineStr">
         <is>
           <t>-45 -43 -45 -43</t>
         </is>
       </c>
-      <c r="L90" t="inlineStr">
+      <c r="L92" t="inlineStr">
         <is>
           <t>+3 -45 -43 -45 -43</t>
         </is>
       </c>
-      <c r="M90" t="inlineStr">
+      <c r="M92" t="inlineStr">
         <is>
           <t>-35 -32 -35 -32</t>
         </is>
       </c>
-      <c r="N90" t="inlineStr">
+      <c r="N92" t="inlineStr">
         <is>
           <t>-34 -35 -32 -35 -32</t>
         </is>
       </c>
-      <c r="O90" t="inlineStr">
+      <c r="O92" t="inlineStr">
         <is>
           <t>-35 -32 -35 -32</t>
         </is>
       </c>
-      <c r="P90" t="inlineStr">
+      <c r="P92" t="inlineStr">
         <is>
           <t>-34 -35 -32 -35 -32</t>
         </is>
       </c>
-      <c r="Q90" t="inlineStr">
+      <c r="Q92" t="inlineStr">
         <is>
           <t>10,10,10,10</t>
         </is>
       </c>
-      <c r="R90" t="inlineStr">
+      <c r="R92" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="S90" t="inlineStr">
+      <c r="S92" t="inlineStr">
         <is>
           <t>35,10,10,10,10</t>
         </is>
       </c>
-      <c r="T90" t="inlineStr">
+      <c r="T92" t="inlineStr">
         <is>
           <t>llll</t>
         </is>
       </c>
-      <c r="U90" t="inlineStr">
+      <c r="U92" t="inlineStr">
         <is>
           <t>Mllll</t>
         </is>
       </c>
-      <c r="AA90" t="inlineStr">
+      <c r="AA92" t="inlineStr">
         <is>
           <t>1e575213-1523-40b8-9492-0a92235d1799</t>
         </is>
       </c>
-      <c r="AB90" t="inlineStr">
+      <c r="AB92" t="inlineStr">
         <is>
           <t>71c8d35f-24b6-430d-abc5-2ff4c47a8f3b</t>
         </is>
       </c>
-      <c r="AC90" t="inlineStr">
+      <c r="AC92" t="inlineStr">
         <is>
           <t>421087d9-77e4-4344-95d3-0ffee0325022</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="B91" t="inlineStr">
+    <row r="93">
+      <c r="B93" t="inlineStr">
         <is>
           <t>KND d+1+2</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
+      <c r="C93" t="inlineStr">
         <is>
           <t>KND d+1+2</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
+      <c r="E93" t="inlineStr">
         <is>
           <t>Spring Hammer - Sit Down</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
+      <c r="F93" t="inlineStr">
         <is>
           <t>Spring Hammer - Sit Down</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
+      <c r="H93" t="inlineStr">
         <is>
           <t>1 1</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr">
+      <c r="K93" t="inlineStr">
         <is>
           <t>+20</t>
         </is>
       </c>
-      <c r="L91" t="inlineStr">
+      <c r="L93" t="inlineStr">
         <is>
           <t>+20</t>
         </is>
       </c>
-      <c r="M91" t="inlineStr">
+      <c r="M93" t="inlineStr">
         <is>
           <t>+14</t>
         </is>
       </c>
-      <c r="N91" t="inlineStr">
+      <c r="N93" t="inlineStr">
         <is>
           <t>+14</t>
         </is>
       </c>
-      <c r="O91" t="inlineStr">
+      <c r="O93" t="inlineStr">
         <is>
           <t>+14</t>
         </is>
       </c>
-      <c r="P91" t="inlineStr">
+      <c r="P93" t="inlineStr">
         <is>
           <t>+14</t>
         </is>
       </c>
-      <c r="Q91" t="inlineStr">
+      <c r="Q93" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R91" t="inlineStr">
+      <c r="R93" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S91" t="inlineStr">
+      <c r="S93" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="T91" t="inlineStr">
+      <c r="T93" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U91" t="inlineStr">
+      <c r="U93" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="AA91" t="inlineStr">
+      <c r="AA93" t="inlineStr">
         <is>
           <t>9ea7e1a3-859f-438a-b3fc-0ff0de0e315f</t>
         </is>
       </c>
-      <c r="AB91" t="inlineStr">
+      <c r="AB93" t="inlineStr">
         <is>
           <t>0066d9e6-44cc-4c22-b95a-1c01b1cb1dcb</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="B92" t="inlineStr">
+    <row r="94">
+      <c r="B94" t="inlineStr">
         <is>
           <t>– 1,2,1,2</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
+      <c r="C94" t="inlineStr">
         <is>
           <t>KND d+1+2 ,1 ,2 ,1 ,2</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
+      <c r="E94" t="inlineStr">
         <is>
           <t>– Sitting Punches</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
+      <c r="F94" t="inlineStr">
         <is>
           <t>Spring Hammer - Sit Down – Sitting Punches</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
+      <c r="H94" t="inlineStr">
         <is>
           <t>1 1 1 1 1 1</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr">
+      <c r="I94" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr">
+      <c r="K94" t="inlineStr">
         <is>
           <t>-45 -43 -45 -43</t>
         </is>
       </c>
-      <c r="L92" t="inlineStr">
+      <c r="L94" t="inlineStr">
         <is>
           <t>+20 -45 -43 -45 -43</t>
         </is>
       </c>
-      <c r="M92" t="inlineStr">
+      <c r="M94" t="inlineStr">
         <is>
           <t>-35 -32 -35 -32</t>
         </is>
       </c>
-      <c r="N92" t="inlineStr">
+      <c r="N94" t="inlineStr">
         <is>
           <t>+14 -35 -32 -35 -32</t>
         </is>
       </c>
-      <c r="O92" t="inlineStr">
+      <c r="O94" t="inlineStr">
         <is>
           <t>-35 -32 -35 -32</t>
         </is>
       </c>
-      <c r="P92" t="inlineStr">
+      <c r="P94" t="inlineStr">
         <is>
           <t>+14 -35 -32 -35 -32</t>
         </is>
       </c>
-      <c r="Q92" t="inlineStr">
+      <c r="Q94" t="inlineStr">
         <is>
           <t>10,10,10,10</t>
         </is>
       </c>
-      <c r="R92" t="inlineStr">
+      <c r="R94" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="S92" t="inlineStr">
+      <c r="S94" t="inlineStr">
         <is>
           <t>12,10,10,10,10</t>
         </is>
       </c>
-      <c r="T92" t="inlineStr">
+      <c r="T94" t="inlineStr">
         <is>
           <t>llll</t>
         </is>
       </c>
-      <c r="U92" t="inlineStr">
+      <c r="U94" t="inlineStr">
         <is>
           <t>mllll</t>
         </is>
       </c>
-      <c r="AA92" t="inlineStr">
+      <c r="AA94" t="inlineStr">
         <is>
           <t>eb0c424e-d4b0-438e-bfb7-164bbca1894a</t>
         </is>
       </c>
-      <c r="AB92" t="inlineStr">
+      <c r="AB94" t="inlineStr">
         <is>
           <t>01e88eb2-b793-4ba3-9d87-7f7b3ab33381</t>
         </is>
       </c>
-      <c r="AC92" t="inlineStr">
+      <c r="AC94" t="inlineStr">
         <is>
           <t>9ea7e1a3-859f-438a-b3fc-0ff0de0e315f</t>
         </is>
       </c>
     </row>
-    <row r="93"/>
-    <row r="94">
-      <c r="A94" s="1" t="inlineStr">
+    <row r="95"/>
+    <row r="96">
+      <c r="A96" s="1" t="inlineStr">
         <is>
           <t>Unblockable Arts</t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="1" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="1" t="inlineStr">
         <is>
           <t>From Stance</t>
         </is>
       </c>
-      <c r="B95" s="1" t="inlineStr">
+      <c r="B97" s="1" t="inlineStr">
         <is>
           <t>Command</t>
         </is>
       </c>
-      <c r="C95" s="1" t="inlineStr">
+      <c r="C97" s="1" t="inlineStr">
         <is>
           <t>Command Full</t>
         </is>
       </c>
-      <c r="D95" s="1" t="inlineStr">
+      <c r="D97" s="1" t="inlineStr">
         <is>
           <t>Alt Commands</t>
         </is>
       </c>
-      <c r="E95" s="1" t="inlineStr">
+      <c r="E97" s="1" t="inlineStr">
         <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="F95" s="1" t="inlineStr">
+      <c r="F97" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="G95" s="1" t="inlineStr">
+      <c r="G97" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="H95" s="1" t="inlineStr">
+      <c r="H97" s="1" t="inlineStr">
         <is>
           <t>Hits Per Move</t>
         </is>
       </c>
-      <c r="I95" s="1" t="inlineStr">
+      <c r="I97" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="J95" s="1" t="inlineStr">
+      <c r="J97" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="K95" s="1" t="inlineStr">
+      <c r="K97" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="L95" s="1" t="inlineStr">
+      <c r="L97" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="M95" s="1" t="inlineStr">
+      <c r="M97" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="N95" s="1" t="inlineStr">
+      <c r="N97" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="O95" s="1" t="inlineStr">
+      <c r="O97" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="P95" s="1" t="inlineStr">
+      <c r="P97" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="Q95" s="1" t="inlineStr">
+      <c r="Q97" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="R95" s="1" t="inlineStr">
+      <c r="R97" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="S95" s="1" t="inlineStr">
+      <c r="S97" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="T95" s="1" t="inlineStr">
+      <c r="T97" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="U95" s="1" t="inlineStr">
+      <c r="U97" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="V95" s="1" t="inlineStr">
+      <c r="V97" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="W95" s="1" t="inlineStr">
+      <c r="W97" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="X95" s="1" t="inlineStr">
+      <c r="X97" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="Y95" s="1" t="inlineStr">
+      <c r="Y97" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="Z95" s="1" t="inlineStr">
+      <c r="Z97" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="AA95" s="1" t="inlineStr">
+      <c r="AA97" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="AB95" s="1" t="inlineStr">
+      <c r="AB97" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AC95" s="1" t="inlineStr">
+      <c r="AC97" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AD95" s="1" t="inlineStr">
+      <c r="AD97" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>hcf</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>hcf</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>b,b+1</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>Gigaton Start Up</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Gigaton Start Up</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Q96" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R96" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S96" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T96" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="U96" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA96" t="inlineStr">
-        <is>
-          <t>d1938783-b653-4c21-91d7-5303ce4b61cb</t>
-        </is>
-      </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>67a32d45-116c-42ad-88df-89b38e4ca9aa</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>– b,db,d,df,f,uf,u,ub</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>hcf,b,db,d,df,f,uf,u,ub</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>– Wind Up</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>Gigaton Start Up – Wind Up</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Q97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S97" t="inlineStr">
-        <is>
-          <t>-,-</t>
-        </is>
-      </c>
-      <c r="T97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="U97" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="Y97" t="inlineStr">
-        <is>
-          <t>Can be repeated up to 5 times.</t>
-        </is>
-      </c>
-      <c r="AA97" t="inlineStr">
-        <is>
-          <t>1f65d946-be2a-4bb4-9a27-18e4ad27b7a8</t>
-        </is>
-      </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>99aa8796-5bbe-4d4a-8523-9278daf2c772</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>d1938783-b653-4c21-91d7-5303ce4b61cb</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="B98" t="inlineStr">
         <is>
+          <t>hcf</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>hcf</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>b,b+1</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Gigaton Start Up</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Gigaton Start Up</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>d1938783-b653-4c21-91d7-5303ce4b61cb</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>67a32d45-116c-42ad-88df-89b38e4ca9aa</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>– b,db,d,df,f,uf,u,ub</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>hcf,b,db,d,df,f,uf,u,ub</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>– Wind Up</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Gigaton Start Up – Wind Up</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>-,-</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>Can be repeated up to 5 times.</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>1f65d946-be2a-4bb4-9a27-18e4ad27b7a8</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>99aa8796-5bbe-4d4a-8523-9278daf2c772</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>d1938783-b653-4c21-91d7-5303ce4b61cb</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" t="inlineStr">
+        <is>
           <t>–– 1</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
+      <c r="C100" t="inlineStr">
         <is>
           <t>hcf,b,db,d,df,f,uf,u,ub,1</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
+      <c r="E100" t="inlineStr">
         <is>
           <t>–– Gigaton Punch</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
+      <c r="F100" t="inlineStr">
         <is>
           <t>Gigaton Start Up – Wind Up – Gigaton Punch</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
+      <c r="H100" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr">
+      <c r="K100" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L98" t="inlineStr">
+      <c r="L100" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M98" t="inlineStr">
+      <c r="M100" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N98" t="inlineStr">
+      <c r="N100" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O98" t="inlineStr">
+      <c r="O100" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P98" t="inlineStr">
+      <c r="P100" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="Q98" t="inlineStr">
+      <c r="Q100" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="R98" t="inlineStr">
+      <c r="R100" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="S98" t="inlineStr">
+      <c r="S100" t="inlineStr">
         <is>
           <t>-,-,40</t>
         </is>
       </c>
-      <c r="T98" t="inlineStr">
+      <c r="T100" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="U98" t="inlineStr">
+      <c r="U100" t="inlineStr">
         <is>
           <t>--!</t>
         </is>
       </c>
-      <c r="Y98" t="inlineStr">
+      <c r="Y100" t="inlineStr">
         <is>
           <t>Damage increases to 60, 80 and 199 with each extra Wind Up. Becomes Unblockable after 2 Wind Ups.</t>
         </is>
       </c>
-      <c r="AA98" t="inlineStr">
+      <c r="AA100" t="inlineStr">
         <is>
           <t>5effdb03-d23f-4671-8daa-b173c35d0ee4</t>
         </is>
       </c>
-      <c r="AB98" t="inlineStr">
+      <c r="AB100" t="inlineStr">
         <is>
           <t>8ae507ae-80ca-4f99-8564-71283564636c</t>
         </is>
       </c>
-      <c r="AC98" t="inlineStr">
+      <c r="AC100" t="inlineStr">
         <is>
           <t>1f65d946-be2a-4bb4-9a27-18e4ad27b7a8</t>
         </is>
       </c>
     </row>
-    <row r="99"/>
-    <row r="100">
-      <c r="A100" s="1" t="inlineStr">
+    <row r="101"/>
+    <row r="102">
+      <c r="A102" s="1" t="inlineStr">
         <is>
           <t>String Hit Arts</t>
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="1" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="1" t="inlineStr">
         <is>
           <t>From Stance</t>
         </is>
       </c>
-      <c r="B101" s="1" t="inlineStr">
+      <c r="B103" s="1" t="inlineStr">
         <is>
           <t>Command</t>
         </is>
       </c>
-      <c r="C101" s="1" t="inlineStr">
+      <c r="C103" s="1" t="inlineStr">
         <is>
           <t>Command Full</t>
         </is>
       </c>
-      <c r="D101" s="1" t="inlineStr">
+      <c r="D103" s="1" t="inlineStr">
         <is>
           <t>Alt Commands</t>
         </is>
       </c>
-      <c r="E101" s="1" t="inlineStr">
+      <c r="E103" s="1" t="inlineStr">
         <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="F101" s="1" t="inlineStr">
+      <c r="F103" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="G101" s="1" t="inlineStr">
+      <c r="G103" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="H101" s="1" t="inlineStr">
+      <c r="H103" s="1" t="inlineStr">
         <is>
           <t>Hits Per Move</t>
         </is>
       </c>
-      <c r="I101" s="1" t="inlineStr">
+      <c r="I103" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="J101" s="1" t="inlineStr">
+      <c r="J103" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="K101" s="1" t="inlineStr">
+      <c r="K103" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="L101" s="1" t="inlineStr">
+      <c r="L103" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="M101" s="1" t="inlineStr">
+      <c r="M103" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="N101" s="1" t="inlineStr">
+      <c r="N103" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="O101" s="1" t="inlineStr">
+      <c r="O103" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="P101" s="1" t="inlineStr">
+      <c r="P103" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="Q101" s="1" t="inlineStr">
+      <c r="Q103" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="R101" s="1" t="inlineStr">
+      <c r="R103" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="S101" s="1" t="inlineStr">
+      <c r="S103" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="T101" s="1" t="inlineStr">
+      <c r="T103" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="U101" s="1" t="inlineStr">
+      <c r="U103" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="V101" s="1" t="inlineStr">
+      <c r="V103" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="W101" s="1" t="inlineStr">
+      <c r="W103" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="X101" s="1" t="inlineStr">
+      <c r="X103" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="Y101" s="1" t="inlineStr">
+      <c r="Y103" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="Z101" s="1" t="inlineStr">
+      <c r="Z103" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="AA101" s="1" t="inlineStr">
+      <c r="AA103" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="AB101" s="1" t="inlineStr">
+      <c r="AB103" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AC101" s="1" t="inlineStr">
+      <c r="AC103" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AD101" s="1" t="inlineStr">
+      <c r="AD103" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>D+2,1,1,1,2,1,2,1,1+2,1+2</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>D+2 ,1 ,1 ,1 ,2 ,1 ,2 ,1 ,1+2 ,1+2</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>1 1 1 1 1 1 1 1 1 1</t>
-        </is>
-      </c>
-      <c r="Q102" t="inlineStr">
-        <is>
-          <t>10,6,5,7,7,6,6,8,21,25</t>
-        </is>
-      </c>
-      <c r="R102" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="S102" t="inlineStr">
-        <is>
-          <t>10,6,5,7,7,6,6,8,21,25</t>
-        </is>
-      </c>
-      <c r="T102" t="inlineStr">
-        <is>
-          <t>sLLmmmmmmm</t>
-        </is>
-      </c>
-      <c r="U102" t="inlineStr">
-        <is>
-          <t>sLLmmmmmmm</t>
-        </is>
-      </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>cedd2a7b-61d7-42fe-9349-42a2b1503d3f</t>
-        </is>
-      </c>
-      <c r="AD102" t="inlineStr">
-        <is>
-          <t>ML only</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>D+2,1,1,1,2,1,2,1,d+1+2,1+2</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>D+2 ,1 ,1 ,1 ,2 ,1 ,2 ,1 ,d+1+2 ,1+2</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>1 1 1 1 1 1 1 1 1 1</t>
-        </is>
-      </c>
-      <c r="Q103" t="inlineStr">
-        <is>
-          <t>10,6,5,7,7,6,6,8,12,35</t>
-        </is>
-      </c>
-      <c r="R103" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="S103" t="inlineStr">
-        <is>
-          <t>10,6,5,7,7,6,6,8,12,35</t>
-        </is>
-      </c>
-      <c r="T103" t="inlineStr">
-        <is>
-          <t>sLLmmmmmlm</t>
-        </is>
-      </c>
-      <c r="U103" t="inlineStr">
-        <is>
-          <t>sLLmmmmmlm</t>
-        </is>
-      </c>
-      <c r="AB103" t="inlineStr">
-        <is>
-          <t>46414757-6bbc-43ff-bcce-43bb3e815b75</t>
-        </is>
-      </c>
-      <c r="AD103" t="inlineStr">
-        <is>
-          <t>ML only</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="B104" t="inlineStr">
         <is>
-          <t>uf+1,1,4,3,4,1,2,1,1+2,1+2</t>
+          <t>D+2,1,1,1,2,1,2,1,1+2,1+2</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>uf+1 ,1 ,4 ,3 ,4 ,1 ,2 ,1 ,1+2 ,1+2</t>
+          <t>D+2 ,1 ,1 ,1 ,2 ,1 ,2 ,1 ,1+2 ,1+2</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -9747,32 +9827,32 @@
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>15,8,5,5,5,8,6,8,21,25</t>
+          <t>10,6,5,7,7,6,6,8,21,25</t>
         </is>
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>101</t>
         </is>
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>15,8,5,5,5,8,6,8,21,25</t>
+          <t>10,6,5,7,7,6,6,8,21,25</t>
         </is>
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>hmLLLmmmmm</t>
+          <t>sLLmmmmmmm</t>
         </is>
       </c>
       <c r="U104" t="inlineStr">
         <is>
-          <t>hmLLLmmmmm</t>
+          <t>sLLmmmmmmm</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>66ed2d10-6ef0-489d-ad01-ab4680052d18</t>
+          <t>cedd2a7b-61d7-42fe-9349-42a2b1503d3f</t>
         </is>
       </c>
       <c r="AD104" t="inlineStr">
@@ -9784,50 +9864,154 @@
     <row r="105">
       <c r="B105" t="inlineStr">
         <is>
+          <t>D+2,1,1,1,2,1,2,1,d+1+2,1+2</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>D+2 ,1 ,1 ,1 ,2 ,1 ,2 ,1 ,d+1+2 ,1+2</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>1 1 1 1 1 1 1 1 1 1</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>10,6,5,7,7,6,6,8,12,35</t>
+        </is>
+      </c>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>10,6,5,7,7,6,6,8,12,35</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>sLLmmmmmlm</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>sLLmmmmmlm</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>46414757-6bbc-43ff-bcce-43bb3e815b75</t>
+        </is>
+      </c>
+      <c r="AD105" t="inlineStr">
+        <is>
+          <t>ML only</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>uf+1,1,4,3,4,1,2,1,1+2,1+2</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>uf+1 ,1 ,4 ,3 ,4 ,1 ,2 ,1 ,1+2 ,1+2</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>1 1 1 1 1 1 1 1 1 1</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>15,8,5,5,5,8,6,8,21,25</t>
+        </is>
+      </c>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>15,8,5,5,5,8,6,8,21,25</t>
+        </is>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>hmLLLmmmmm</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>hmLLLmmmmm</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>66ed2d10-6ef0-489d-ad01-ab4680052d18</t>
+        </is>
+      </c>
+      <c r="AD106" t="inlineStr">
+        <is>
+          <t>ML only</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="B107" t="inlineStr">
+        <is>
           <t>uf+1,1,4,3,4,12,1,d+1+2,1+2</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
+      <c r="C107" t="inlineStr">
         <is>
           <t>uf+1 ,1 ,4 ,3 ,4 ,12 ,1 ,d+1+2 ,1+2</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
+      <c r="H107" t="inlineStr">
         <is>
           <t>1 1 1 1 1 1 1 1 1</t>
         </is>
       </c>
-      <c r="Q105" t="inlineStr">
+      <c r="Q107" t="inlineStr">
         <is>
           <t>15,8,5,5,5,8,6,8,12,35</t>
         </is>
       </c>
-      <c r="R105" t="inlineStr">
+      <c r="R107" t="inlineStr">
         <is>
           <t>107</t>
         </is>
       </c>
-      <c r="S105" t="inlineStr">
+      <c r="S107" t="inlineStr">
         <is>
           <t>15,8,5,5,5,8,6,8,12,35</t>
         </is>
       </c>
-      <c r="T105" t="inlineStr">
+      <c r="T107" t="inlineStr">
         <is>
           <t>hmLLLmmmlm</t>
         </is>
       </c>
-      <c r="U105" t="inlineStr">
+      <c r="U107" t="inlineStr">
         <is>
           <t>hmLLLmmmlm</t>
         </is>
       </c>
-      <c r="AB105" t="inlineStr">
+      <c r="AB107" t="inlineStr">
         <is>
           <t>bfdf582e-6190-406a-b25c-eee25e104050</t>
         </is>
       </c>
-      <c r="AD105" t="inlineStr">
+      <c r="AD107" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>

--- a/sources/jack2_step10.xlsx
+++ b/sources/jack2_step10.xlsx
@@ -1191,6 +1191,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>19394d42-3833-4c2e-b3ec-46368a6b07eb</t>
+        </is>
+      </c>
       <c r="AB10" t="inlineStr">
         <is>
           <t>19394d42-3833-4c2e-b3ec-46368a6b07eb</t>
@@ -1268,6 +1273,11 @@
           <t>Pressing 1+3 from the side or back will result in a Hell Press, but it doesn't connect as a throw.</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>cb4f10b6-ee04-4947-a9bf-2a0a355cad60</t>
+        </is>
+      </c>
       <c r="AB11" t="inlineStr">
         <is>
           <t>cb4f10b6-ee04-4947-a9bf-2a0a355cad60</t>
@@ -1340,6 +1350,11 @@
           <t>Pressing 1+3 from the side or back will result in a Hell Press, but it doesn't connect as a throw.</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>70ae82e4-7899-4172-9bbc-2145108370e7</t>
+        </is>
+      </c>
       <c r="AB12" t="inlineStr">
         <is>
           <t>70ae82e4-7899-4172-9bbc-2145108370e7</t>
@@ -1415,6 +1430,11 @@
       <c r="Z13" t="inlineStr">
         <is>
           <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>052a3efc-5cdf-4aa6-9af6-a58c6ed3b504</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -9850,6 +9870,11 @@
           <t>sLLmmmmmmm</t>
         </is>
       </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>cedd2a7b-61d7-42fe-9349-42a2b1503d3f</t>
+        </is>
+      </c>
       <c r="AB104" t="inlineStr">
         <is>
           <t>cedd2a7b-61d7-42fe-9349-42a2b1503d3f</t>
@@ -9902,6 +9927,11 @@
           <t>sLLmmmmmlm</t>
         </is>
       </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>46414757-6bbc-43ff-bcce-43bb3e815b75</t>
+        </is>
+      </c>
       <c r="AB105" t="inlineStr">
         <is>
           <t>46414757-6bbc-43ff-bcce-43bb3e815b75</t>
@@ -9954,6 +9984,11 @@
           <t>hmLLLmmmmm</t>
         </is>
       </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>66ed2d10-6ef0-489d-ad01-ab4680052d18</t>
+        </is>
+      </c>
       <c r="AB106" t="inlineStr">
         <is>
           <t>66ed2d10-6ef0-489d-ad01-ab4680052d18</t>
@@ -10004,6 +10039,11 @@
       <c r="U107" t="inlineStr">
         <is>
           <t>hmLLLmmmlm</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>bfdf582e-6190-406a-b25c-eee25e104050</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">

--- a/sources/jack2_step10.xlsx
+++ b/sources/jack2_step10.xlsx
@@ -432,9 +432,9 @@
     <col hidden="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col hidden="1" min="12" max="12"/>
-    <col width="21" customWidth="1" min="13" max="13"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
     <col hidden="1" min="14" max="14"/>
-    <col width="21" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
     <col hidden="1" min="16" max="16"/>
     <col width="22" customWidth="1" min="17" max="17"/>
     <col width="24" customWidth="1" min="18" max="18"/>
@@ -8402,32 +8402,32 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>-20 -22 -20 -22...</t>
+          <t>-20 -22 -20 -22 -20 -22</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>-20 -22 -20 -22...</t>
+          <t>-20 -22 -20 -22 -20 -22</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>-9 -11 -9 -11...</t>
+          <t>-9 -11 -9 -11 -9 -11</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>-9 -11 -9 -11...</t>
+          <t>-9 -11 -9 -11 -9 -11</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>-9 -11 -9 -11...</t>
+          <t>-9 -11 -9 -11 -9 -11</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>-9 -11 -9 -11...</t>
+          <t>-9 -11 -9 -11 -9 -11</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
@@ -8673,7 +8673,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>1 1</t>
+          <t>0 1</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -8795,7 +8795,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>1 1 1 1 1</t>
+          <t>0 1 1 1 1</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">

--- a/sources/jack2_step10.xlsx
+++ b/sources/jack2_step10.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE104"/>
+  <dimension ref="A1:AE109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -426,7 +426,7 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col hidden="1" min="6" max="6"/>
-    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="53" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col hidden="1" min="10" max="10"/>
@@ -4523,6 +4523,16 @@
           <t>b,db,d,DF+1</t>
         </is>
       </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>hcf,DF+1</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>hcf,DF+1</t>
+        </is>
+      </c>
       <c r="F49" t="inlineStr">
         <is>
           <t>Debugger</t>
@@ -4642,40 +4652,20 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Wind Up</t>
+          <t>Wind Up (1 Rotation)</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Wind Up</t>
+          <t>Wind Up (1 Rotation)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R50" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="V50" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4704,12 +4694,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gigaton Punch</t>
+          <t>– Gigaton Punch (1 Rotation)</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Wind Up – Gigaton Punch</t>
+          <t>Wind Up (1 Rotation) – Gigaton Punch (1 Rotation)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -4764,7 +4754,7 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>-,20</t>
+          <t>20</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -4774,7 +4764,7 @@
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>-m</t>
+          <t>m</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
@@ -4801,321 +4791,166 @@
     <row r="52">
       <c r="B52" t="inlineStr">
         <is>
-          <t>– DF+1</t>
+          <t>ccw,db,d</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>hcf,DF+1</t>
+          <t>ccw,db,d</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Debugger</t>
+          <t>Wind Up (2 Rotations)</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Wind Up – Debugger</t>
+          <t>Wind Up (2 Rotations)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>-45</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>-45</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="Q52" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="R52" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>-,25</t>
-        </is>
-      </c>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="V52" t="inlineStr">
-        <is>
-          <t>-L</t>
-        </is>
-      </c>
-      <c r="Y52" t="inlineStr">
-        <is>
-          <t>RC</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>With b,b+1 input, full 2nd rotation command is b,b+1,b,db,d,df</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>bfcd8070-9fe9-4f68-b19e-bddec360b30a</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>bc7743df-d62c-4baf-90d6-ca367a954aba</t>
-        </is>
-      </c>
-      <c r="AD52" t="inlineStr">
-        <is>
-          <t>c03fb65b-aaac-4006-8e2b-0a9f8c08fd8f</t>
+          <t>1f65d946-be2a-4bb4-9a27-18e4ad27b7a8</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="B53" t="inlineStr">
         <is>
-          <t>DF+1,2,1,2</t>
+          <t>– 1</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>DF+1 ,2 ,1 ,2</t>
+          <t>ccw,db,d,1</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Uppercut Rush</t>
+          <t>– Gigaton Punch (2 Rotations)</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Uppercut Rush</t>
+          <t>Wind Up (2 Rotations) – Gigaton Punch (2 Rotations)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>1 1 1 1</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>-11 -7 -9 -2</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>-11 -7 -9 -2</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>KD +4 +2 +9</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>KD +4 +2 +9</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>KD +4 +2 +9</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>KD +4 +2 +9</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>10,15,10,15</t>
+          <t>40</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>40</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>10,15,10,15</t>
+          <t>40</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>mmmm</t>
+          <t>!</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>mmmm</t>
-        </is>
-      </c>
-      <c r="Y53" t="inlineStr">
-        <is>
-          <t>JGc RC</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>Juggles on the last hit if the first hit was a counter hit.</t>
+          <t>!</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>4f881878-519e-4f9f-bb13-ebe8511b7e9f</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>bf72dea8-4c41-4bb6-9420-9305240a53e3</t>
+          <t>5effdb03-d23f-4671-8daa-b173c35d0ee4</t>
+        </is>
+      </c>
+      <c r="AD53" t="inlineStr">
+        <is>
+          <t>1f65d946-be2a-4bb4-9a27-18e4ad27b7a8</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="B54" t="inlineStr">
         <is>
-          <t>FC+df+1,2,1</t>
+          <t>ccw,ccw,db,d</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>FC+df+1 ,2 ,1</t>
+          <t>ccw,ccw,db,d</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Windmill</t>
+          <t>Wind Up (3 Rotations)</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Windmill</t>
+          <t>Wind Up (3 Rotations)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>1 1 1</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>-22 -22 -2</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>-22 -22 -2</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>-12 -12 -12</t>
-        </is>
-      </c>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t>-12 -12 -12</t>
-        </is>
-      </c>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>-12 -12 -12</t>
-        </is>
-      </c>
-      <c r="Q54" t="inlineStr">
-        <is>
-          <t>-12 -12 -12</t>
-        </is>
-      </c>
-      <c r="R54" t="inlineStr">
-        <is>
-          <t>10,15,10</t>
-        </is>
-      </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>10,15,10</t>
-        </is>
-      </c>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t>mmm</t>
-        </is>
-      </c>
-      <c r="V54" t="inlineStr">
-        <is>
-          <t>mmm</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>With b,b+1 input, full 3rd rotation command is b,b+1,ccw,b,db,d</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>dbb96ec3-9f0f-4e57-b4ca-8de7e5046661</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>1c7f46c4-6ab3-4fdd-90e3-5f642409d3af</t>
+          <t>f6c85458-dd91-4d88-91f1-9a557e0c3420</t>
         </is>
       </c>
     </row>
@@ -5127,37 +4962,32 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>FC+df+1 ,2 ,1 ,1</t>
+          <t>ccw,ccw,db,d,1</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>– Windmill Backhand</t>
+          <t>– Gigaton Punch (3 Rotations)</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Windmill – Windmill Backhand</t>
+          <t>Wind Up (3 Rotations) – Gigaton Punch (3 Rotations)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>1 1 1 1</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>24</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>+20</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>-22 -22 -2 +20</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -5167,7 +4997,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>-12 -12 -12 KD</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -5177,888 +5007,618 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>-12 -12 -12 KD</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>60</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>60</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>10,15,10,30</t>
+          <t>60</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>!</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>mmmh</t>
-        </is>
-      </c>
-      <c r="Y55" t="inlineStr">
-        <is>
-          <t>CF GB</t>
+          <t>!</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>82838a4d-d558-42b7-ab73-e05d17ef4b08</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>e3e5f6b7-4929-4a52-8c31-e6806f1334ee</t>
+          <t>e63a69f8-5fec-47ed-a05a-1068334010ce</t>
         </is>
       </c>
       <c r="AD55" t="inlineStr">
         <is>
-          <t>dbb96ec3-9f0f-4e57-b4ca-8de7e5046661</t>
+          <t>f6c85458-dd91-4d88-91f1-9a557e0c3420</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="B56" t="inlineStr">
         <is>
-          <t>DF,1,2</t>
+          <t>ccw,ccw,ccw,db,d</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>DF,1 ,2</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>FC+DF+1,2</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>FC+DF+1,2</t>
+          <t>ccw,ccw,ccw,db,d</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Medium Hammer Rush</t>
+          <t>Wind Up (4 Rotations)</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Medium Hammer Rush</t>
+          <t>Wind Up (4 Rotations)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>1 1</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>-6 -8</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>-6 -8</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>+5 +2</t>
-        </is>
-      </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>+5 +2</t>
-        </is>
-      </c>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>+5 +2</t>
-        </is>
-      </c>
-      <c r="Q56" t="inlineStr">
-        <is>
-          <t>+5 +2</t>
-        </is>
-      </c>
-      <c r="R56" t="inlineStr">
-        <is>
-          <t>15,12</t>
-        </is>
-      </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>15,12</t>
-        </is>
-      </c>
-      <c r="U56" t="inlineStr">
-        <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="Y56" t="inlineStr">
-        <is>
-          <t>RC</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>fb453abc-0836-42af-adee-dc8f713ceae0</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>53b77124-e72d-4f20-ae78-8225f04ac648</t>
+          <t>c0f65cc6-5cf3-4384-bf35-b9b00543eb08</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="B57" t="inlineStr">
         <is>
-          <t>– d+1</t>
+          <t>– 1</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>DF,1 ,2 ,d+1</t>
+          <t>ccw,ccw,ccw,db,d,1</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>– Low Punch</t>
+          <t>– Gigaton Punch (4 Rotations)</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Medium Hammer Rush – Low Punch</t>
+          <t>Wind Up (4 Rotations) – Gigaton Punch (4 Rotations)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>1 1 1</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>17</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>-6 -8 -17</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>+5 +2 -7</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>+5 +2 -7</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>80</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>80</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>15,12,8</t>
+          <t>80</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>!</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>mmL</t>
-        </is>
-      </c>
-      <c r="Y57" t="inlineStr">
-        <is>
-          <t>RC</t>
+          <t>!</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>29dfa2dc-0160-4e71-b110-03e973136272</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>be700e61-7fed-40b2-a16a-4b062cedd1c9</t>
+          <t>0b650a95-0538-44cb-a60f-505df7041965</t>
         </is>
       </c>
       <c r="AD57" t="inlineStr">
         <is>
-          <t>fb453abc-0836-42af-adee-dc8f713ceae0</t>
+          <t>c0f65cc6-5cf3-4384-bf35-b9b00543eb08</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="B58" t="inlineStr">
         <is>
-          <t>– df+1</t>
+          <t>ccw,ccw,ccw,ccw,db,d</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>DF,1 ,2 ,df+1</t>
+          <t>ccw,ccw,ccw,ccw,db,d</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>– Mid Punch</t>
+          <t>Wind Up (5 Rotations)</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Medium Hammer Rush – Mid Punch</t>
+          <t>Wind Up (5 Rotations)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>1 1 1</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>-6 -8 -1</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>+10</t>
-        </is>
-      </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>+5 +2 +10</t>
-        </is>
-      </c>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>+10</t>
-        </is>
-      </c>
-      <c r="Q58" t="inlineStr">
-        <is>
-          <t>+5 +2 +10</t>
-        </is>
-      </c>
-      <c r="R58" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="T58" t="inlineStr">
-        <is>
-          <t>15,12,15</t>
-        </is>
-      </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>mmm</t>
-        </is>
-      </c>
-      <c r="Y58" t="inlineStr">
-        <is>
-          <t>JGc RC</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>Juggles on the last hit if the first hit was a counter hit.</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>eb9bbfe4-68c3-4e58-baf7-821687138e91</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>636b5aa8-46de-464e-81e9-d0bcfa43dc73</t>
-        </is>
-      </c>
-      <c r="AD58" t="inlineStr">
-        <is>
-          <t>fb453abc-0836-42af-adee-dc8f713ceae0</t>
+          <t>27d20b09-dd03-41a8-a3e5-9fb3bbc279ad</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="B59" t="inlineStr">
         <is>
-          <t>– f+1</t>
+          <t>– 1</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>DF,1 ,2 ,f+1</t>
+          <t>ccw,ccw,ccw,ccw,db,d,1</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>– High Punch</t>
+          <t>– Gigaton Punch (5 Rotations)</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Medium Hammer Rush – High Punch</t>
+          <t>Wind Up (5 Rotations) – Gigaton Punch (5 Rotations)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>1 1 1</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>17</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>-6 -8 -17</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>+5 +2 -5</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>+5 +2 -5</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>199</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>199</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>15,12,12</t>
+          <t>199</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>!</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>mmh</t>
+          <t>!</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>897a7dd1-1093-48ff-85f1-bebca88601ea</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>96ffff19-8555-4463-82fe-458f7c0c053b</t>
+          <t>e17fd2d9-47bc-4541-8a57-8d670b1585de</t>
         </is>
       </c>
       <c r="AD59" t="inlineStr">
         <is>
-          <t>fb453abc-0836-42af-adee-dc8f713ceae0</t>
+          <t>27d20b09-dd03-41a8-a3e5-9fb3bbc279ad</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="B60" t="inlineStr">
         <is>
-          <t>FC+1,1,1,2</t>
+          <t>ccw,ccw,ccw,ccw,ccw,db,d</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>FC+1 ,1 ,1 ,2</t>
+          <t>ccw,ccw,ccw,ccw,ccw,db,d</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Hammer Rush</t>
+          <t>Wind Up (8 Rotations)</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hammer Rush</t>
+          <t>Wind Up (8 Rotations)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>1 1 1 1</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>-8 +1 -12 -8</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>-8 +1 -12 -8</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>+2 +12 -1 +1</t>
-        </is>
-      </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>+2 +12 -1 +1</t>
-        </is>
-      </c>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>+2 +12 -1 +1</t>
-        </is>
-      </c>
-      <c r="Q60" t="inlineStr">
-        <is>
-          <t>+2 +12 -1 +1</t>
-        </is>
-      </c>
-      <c r="R60" t="inlineStr">
-        <is>
-          <t>10,8,12,12</t>
-        </is>
-      </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="T60" t="inlineStr">
-        <is>
-          <t>10,8,12,12</t>
-        </is>
-      </c>
-      <c r="U60" t="inlineStr">
-        <is>
-          <t>LLmm</t>
-        </is>
-      </c>
-      <c r="V60" t="inlineStr">
-        <is>
-          <t>LLmm</t>
-        </is>
-      </c>
-      <c r="Y60" t="inlineStr">
-        <is>
-          <t>RC</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>Completes 8 rotations automatically. No Gigaton Punch follow-up.</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>91a5d27a-8ea9-4505-8341-2bc54479b037</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>87b157c8-bac6-4b55-a543-03b3e5c1c00f</t>
+          <t>15f7632c-c216-4131-a173-898bf20c3023</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="B61" t="inlineStr">
         <is>
-          <t>– d+1</t>
+          <t>DF+1,2,1,2</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>FC+1 ,1 ,1 ,2 ,d+1</t>
+          <t>DF+1 ,2 ,1 ,2</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>– Low Punch</t>
+          <t>Uppercut Rush</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hammer Rush – Low Punch</t>
+          <t>Uppercut Rush</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>1 1 1 1 1</t>
+          <t>1 1 1 1</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>14</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>-11 -7 -9 -2</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>-8 +1 -12 -8 -17</t>
+          <t>-11 -7 -9 -2</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>KD +4 +2 +9</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>+2 +12 -1 +1 -7</t>
+          <t>KD +4 +2 +9</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>KD +4 +2 +9</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>+2 +12 -1 +1 -7</t>
+          <t>KD +4 +2 +9</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10,15,10,15</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>50</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>10,8,12,12,8</t>
+          <t>10,15,10,15</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>mmmm</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>LLmmL</t>
+          <t>mmmm</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>RC</t>
+          <t>JGc RC</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>Juggles on the last hit if the first hit was a counter hit.</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>acb95787-cedc-4b5b-b8fb-50a3e72d4b5b</t>
+          <t>4f881878-519e-4f9f-bb13-ebe8511b7e9f</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>19e50734-0a3e-439a-bb45-d0541eae3da2</t>
-        </is>
-      </c>
-      <c r="AD61" t="inlineStr">
-        <is>
-          <t>91a5d27a-8ea9-4505-8341-2bc54479b037</t>
+          <t>bf72dea8-4c41-4bb6-9420-9305240a53e3</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="B62" t="inlineStr">
         <is>
-          <t>– df+1</t>
+          <t>FC+df+1,2,1</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>FC+1 ,1 ,1 ,2 ,df+1</t>
+          <t>FC+df+1 ,2 ,1</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>– Mid Punch</t>
+          <t>Windmill</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hammer Rush – Mid Punch</t>
+          <t>Windmill</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>1 1 1 1 1</t>
+          <t>1 1 1</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>24</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>24</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-22 -22 -2</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>-8 +1 -12 -8 -1</t>
+          <t>-22 -22 -2</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>+10</t>
+          <t>-12 -12 -12</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>+2 +12 -1 +1 +10</t>
+          <t>-12 -12 -12</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>+10</t>
+          <t>-12 -12 -12</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>+2 +12 -1 +1 +10</t>
+          <t>-12 -12 -12</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10,15,10</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>35</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>10,8,12,12,15</t>
+          <t>10,15,10</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>mmm</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>LLmmm</t>
-        </is>
-      </c>
-      <c r="Y62" t="inlineStr">
-        <is>
-          <t>RC</t>
+          <t>mmm</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>756e1d64-081b-4d25-aaa0-fa5c3b7a738f</t>
+          <t>dbb96ec3-9f0f-4e57-b4ca-8de7e5046661</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>ecd60ebe-4c07-4ca2-a44b-3748905360dd</t>
-        </is>
-      </c>
-      <c r="AD62" t="inlineStr">
-        <is>
-          <t>91a5d27a-8ea9-4505-8341-2bc54479b037</t>
+          <t>1c7f46c4-6ab3-4fdd-90e3-5f642409d3af</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="B63" t="inlineStr">
         <is>
-          <t>– f+1</t>
+          <t>– 1</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>FC+1 ,1 ,1 ,2 ,f+1</t>
+          <t>FC+df+1 ,2 ,1 ,1</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>– High Punch</t>
+          <t>– Windmill Backhand</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hammer Rush – High Punch</t>
+          <t>Windmill – Windmill Backhand</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>1 1 1 1 1</t>
+          <t>1 1 1 1</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>24</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>+20</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>-8 +1 -12 -8 -17</t>
+          <t>-22 -22 -2 +20</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>+2 +12 -1 +1 -5</t>
+          <t>-12 -12 -12 KD</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>+2 +12 -1 +1 -5</t>
+          <t>-12 -12 -12 KD</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>30</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>30</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>10,8,12,12,12</t>
+          <t>10,15,10,30</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -6068,44 +5628,59 @@
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>LLmmh</t>
+          <t>mmmh</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>CF GB</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>ac1b3ebe-7028-47a0-be65-5eb121dab8bc</t>
+          <t>82838a4d-d558-42b7-ab73-e05d17ef4b08</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>fe5b804b-6426-463e-b283-4eb22f9998b3</t>
+          <t>e3e5f6b7-4929-4a52-8c31-e6806f1334ee</t>
         </is>
       </c>
       <c r="AD63" t="inlineStr">
         <is>
-          <t>91a5d27a-8ea9-4505-8341-2bc54479b037</t>
+          <t>dbb96ec3-9f0f-4e57-b4ca-8de7e5046661</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="B64" t="inlineStr">
         <is>
-          <t>FC+1,2</t>
+          <t>DF,1,2</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>FC+1 ,2</t>
+          <t>DF,1 ,2</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>FC+DF+1,2</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>FC+DF+1,2</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Low Punch - Megaton Punch</t>
+          <t>Medium Hammer Rush</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Low Punch - Megaton Punch</t>
+          <t>Medium Hammer Rush</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6115,67 +5690,67 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>-8 -14</t>
+          <t>-6 -8</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>-8 -14</t>
+          <t>-6 -8</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>+2 KD</t>
+          <t>+5 +2</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>+2 KD</t>
+          <t>+5 +2</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>+2 KD</t>
+          <t>+5 +2</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>+2 KD</t>
+          <t>+5 +2</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>10,25</t>
+          <t>15,12</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>27</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>10,25</t>
+          <t>15,12</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>Lm</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>Lm</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr">
@@ -6185,161 +5760,151 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>06ab7954-5d39-49cc-91e3-02c54893dd53</t>
+          <t>fb453abc-0836-42af-adee-dc8f713ceae0</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>a769fb07-8a59-436e-a5fb-3acd34e8e01d</t>
+          <t>53b77124-e72d-4f20-ae78-8225f04ac648</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="B65" t="inlineStr">
         <is>
-          <t>SS+1</t>
+          <t>– d+1</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>SS+1</t>
+          <t>DF,1 ,2 ,d+1</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Jack Hammer</t>
+          <t>– Low Punch</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Jack Hammer</t>
+          <t>Medium Hammer Rush – Low Punch</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>32</t>
+          <t>1 1 1</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-17</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-6 -8 -17</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+5 +2 -7</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+5 +2 -7</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>8</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>8</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15,12,8</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>L</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>mmL</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>BN GB</t>
-        </is>
-      </c>
-      <c r="AA65" t="inlineStr">
-        <is>
-          <t>TRUE</t>
+          <t>RC</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>41456c1a-f3a2-468f-b0ee-ee2032bb78c8</t>
+          <t>29dfa2dc-0160-4e71-b110-03e973136272</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>de86a0e0-55fd-41e5-a239-a7685c39edbd</t>
+          <t>be700e61-7fed-40b2-a16a-4b062cedd1c9</t>
+        </is>
+      </c>
+      <c r="AD65" t="inlineStr">
+        <is>
+          <t>fb453abc-0836-42af-adee-dc8f713ceae0</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="B66" t="inlineStr">
         <is>
-          <t>SS+1+2</t>
+          <t>– df+1</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>SS+1+2</t>
+          <t>DF,1 ,2 ,df+1</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Double Knuckle Swing</t>
+          <t>– Mid Punch</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Double Knuckle Swing</t>
+          <t>Medium Hammer Rush – Mid Punch</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>19</t>
+          <t>1 1 1</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -6349,445 +5914,455 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-6 -8 -1</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+5 +2 +10</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+5 +2 +10</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>15</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>15</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>15,12,15</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>m</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>mmm</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>JGc RC</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>Juggles on the last hit if the first hit was a counter hit.</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15c368e0-8f76-42a0-bbea-ef3cc510e19c</t>
+          <t>eb9bbfe4-68c3-4e58-baf7-821687138e91</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>2f8a7e04-7a60-430d-bc0a-6a55ed0d3427</t>
+          <t>636b5aa8-46de-464e-81e9-d0bcfa43dc73</t>
+        </is>
+      </c>
+      <c r="AD66" t="inlineStr">
+        <is>
+          <t>fb453abc-0836-42af-adee-dc8f713ceae0</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="B67" t="inlineStr">
         <is>
-          <t>1+2&lt;1+2</t>
+          <t>– f+1</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>1+2 &lt;1+2</t>
+          <t>DF,1 ,2 ,f+1</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Hammer Knuckle - Double Uppercut</t>
+          <t>– High Punch</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hammer Knuckle - Double Uppercut</t>
+          <t>Medium Hammer Rush – High Punch</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>1 1</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
+          <t>1 1 1</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>-15 -20</t>
+          <t>-17</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>-15 -20</t>
+          <t>-6 -8 -17</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>KD KD</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>KD KD</t>
+          <t>+5 +2 -5</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>KD KD</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>KD KD</t>
+          <t>+5 +2 -5</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>21,22</t>
+          <t>12</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>12</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>21,22</t>
+          <t>15,12,12</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>h</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="Y67" t="inlineStr">
-        <is>
-          <t>JG</t>
+          <t>mmh</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>54667fc1-c443-4001-a9d7-46c1d391bc4d</t>
+          <t>897a7dd1-1093-48ff-85f1-bebca88601ea</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>36af744c-98c3-48c0-bea9-c96c61093c26</t>
+          <t>96ffff19-8555-4463-82fe-458f7c0c053b</t>
+        </is>
+      </c>
+      <c r="AD67" t="inlineStr">
+        <is>
+          <t>fb453abc-0836-42af-adee-dc8f713ceae0</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="B68" t="inlineStr">
         <is>
-          <t>WS+1+2&lt;1+2</t>
+          <t>FC+1,1,1,2</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>WS+1+2 &lt;1+2</t>
+          <t>FC+1 ,1 ,1 ,2</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Double Uppercut - Hammer Knuckle</t>
+          <t>Hammer Rush</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Double Uppercut - Hammer Knuckle</t>
+          <t>Hammer Rush</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>1 1</t>
+          <t>1 1 1 1</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>-15 -16</t>
+          <t>-8 +1 -12 -8</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>-15 -16</t>
+          <t>-8 +1 -12 -8</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>KD KD</t>
+          <t>+2 +12 -1 +1</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>KD KD</t>
+          <t>+2 +12 -1 +1</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>KD KD</t>
+          <t>+2 +12 -1 +1</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>KD KD</t>
+          <t>+2 +12 -1 +1</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>21,17</t>
+          <t>10,8,12,12</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>42</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>21,17</t>
+          <t>10,8,12,12</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>LLmm</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>LLmm</t>
         </is>
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>RC</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14470b5f-e125-4262-857b-20fa6db24ee3</t>
+          <t>91a5d27a-8ea9-4505-8341-2bc54479b037</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>45985eea-a458-447f-9b9d-941ed088446a</t>
+          <t>87b157c8-bac6-4b55-a543-03b3e5c1c00f</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="B69" t="inlineStr">
         <is>
-          <t>f+1+2</t>
+          <t>– d+1</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>f+1+2</t>
+          <t>FC+1 ,1 ,1 ,2 ,d+1</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Arm Scissors</t>
+          <t>– Low Punch</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Arm Scissors</t>
+          <t>Hammer Rush – Low Punch</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>17</t>
+          <t>1 1 1 1 1</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-17</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-8 +1 -12 -8 -17</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+2 +12 -1 +1 -7</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+2 +12 -1 +1 -7</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>8</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>8</t>
         </is>
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>10,8,12,12,8</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>L</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>LLmmL</t>
         </is>
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>RC</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>fab4def4-7c2d-4882-ac15-2c257a91fc81</t>
+          <t>acb95787-cedc-4b5b-b8fb-50a3e72d4b5b</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>f51b4cde-994c-422f-b3e6-3e932f7d87ff</t>
+          <t>19e50734-0a3e-439a-bb45-d0541eae3da2</t>
+        </is>
+      </c>
+      <c r="AD69" t="inlineStr">
+        <is>
+          <t>91a5d27a-8ea9-4505-8341-2bc54479b037</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="B70" t="inlineStr">
         <is>
-          <t>– 1+2</t>
+          <t>– df+1</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>f+1+2 ,1+2</t>
+          <t>FC+1 ,1 ,1 ,2 ,df+1</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>– Cross Cut Saw</t>
+          <t>– Mid Punch</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Arm Scissors – Cross Cut Saw</t>
+          <t>Hammer Rush – Mid Punch</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>1 1</t>
+          <t>1 1 1 1 1</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>-14</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>-10 -14</t>
+          <t>-8 +1 -12 -8 -1</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>KD KD</t>
+          <t>+2 +12 -1 +1 +10</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>KD KD</t>
+          <t>+2 +12 -1 +1 +10</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
@@ -6802,17 +6377,17 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>17,15</t>
+          <t>10,8,12,12,15</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>l</t>
+          <t>m</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>LLmmm</t>
         </is>
       </c>
       <c r="Y70" t="inlineStr">
@@ -6822,263 +6397,248 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>acab70ca-8813-48c6-907e-58ba82b57685</t>
+          <t>756e1d64-081b-4d25-aaa0-fa5c3b7a738f</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>e7af4cd0-902b-4b89-9c43-ea9365bec42c</t>
+          <t>ecd60ebe-4c07-4ca2-a44b-3748905360dd</t>
         </is>
       </c>
       <c r="AD70" t="inlineStr">
         <is>
-          <t>fab4def4-7c2d-4882-ac15-2c257a91fc81</t>
+          <t>91a5d27a-8ea9-4505-8341-2bc54479b037</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="B71" t="inlineStr">
         <is>
-          <t>– ~df+2</t>
+          <t>– f+1</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>f+1+2 ~df+2</t>
+          <t>FC+1 ,1 ,1 ,2 ,f+1</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>– Megaton Punch</t>
+          <t>– High Punch</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Arm Scissors – Megaton Punch</t>
+          <t>Hammer Rush – High Punch</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>1 1</t>
+          <t>1 1 1 1 1</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>-19</t>
+          <t>-17</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>-10 -19</t>
+          <t>-8 +1 -12 -8 -17</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>KD KD</t>
+          <t>+2 +12 -1 +1 -5</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>KD KD</t>
+          <t>+2 +12 -1 +1 -5</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>12</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>12</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>17,25</t>
+          <t>10,8,12,12,12</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>h</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="Y71" t="inlineStr">
-        <is>
-          <t>RC</t>
+          <t>LLmmh</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>773af138-28f0-48ff-9b0e-97e83d2d8d3f</t>
+          <t>ac1b3ebe-7028-47a0-be65-5eb121dab8bc</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>b671f9fe-a460-4157-8300-00379e99322d</t>
+          <t>fe5b804b-6426-463e-b283-4eb22f9998b3</t>
         </is>
       </c>
       <c r="AD71" t="inlineStr">
         <is>
-          <t>fab4def4-7c2d-4882-ac15-2c257a91fc81</t>
+          <t>91a5d27a-8ea9-4505-8341-2bc54479b037</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="B72" t="inlineStr">
         <is>
-          <t>d+1+2</t>
+          <t>FC+1,2</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>d+1+2</t>
+          <t>FC+1 ,2</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Bravo Knuckle</t>
+          <t>Low Punch - Megaton Punch</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Bravo Knuckle</t>
+          <t>Low Punch - Megaton Punch</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1 1</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>19</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>-23</t>
+          <t>-8 -14</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>-23</t>
+          <t>-8 -14</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+2 KD</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+2 KD</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+2 KD</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+2 KD</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>10,25</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>35</t>
         </is>
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>10,25</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>Lm</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>Lm</t>
         </is>
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>JG GB</t>
-        </is>
-      </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>When tagging in Bryan Fury hit 2 to grab the opponent in mid air and do a Fisherman's Slam. Total damage is 21,21.</t>
-        </is>
-      </c>
-      <c r="AA72" t="inlineStr">
-        <is>
-          <t>TRUE</t>
+          <t>RC</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>f79bf7d8-dcd1-4a58-883f-38e113a7b9e1</t>
+          <t>06ab7954-5d39-49cc-91e3-02c54893dd53</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>2ecc5ad9-b4ca-485a-884a-0301a91b3509</t>
+          <t>a769fb07-8a59-436e-a5fb-3acd34e8e01d</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="B73" t="inlineStr">
         <is>
-          <t>FC+1+2</t>
+          <t>SS+1</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>FC+1+2</t>
+          <t>SS+1</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Cross Cut Saw</t>
+          <t>Jack Hammer</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cross Cut Saw</t>
+          <t>Jack Hammer</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7088,22 +6648,22 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>32</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>-19</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>-19</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -7128,587 +6688,557 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>l</t>
+          <t>m</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>l</t>
+          <t>m</t>
         </is>
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>RC</t>
+          <t>BN GB</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>23e71f4e-0ab8-4ddc-89c1-4b2fe81234cc</t>
+          <t>41456c1a-f3a2-468f-b0ee-ee2032bb78c8</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>52606470-ef56-4c68-a311-9fe12c9a5f23</t>
+          <t>de86a0e0-55fd-41e5-a239-a7685c39edbd</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="B74" t="inlineStr">
         <is>
-          <t>DF,2,1,2</t>
+          <t>SS+1+2</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>DF,2 ,1 ,2</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>FC+DF+2,1,2</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>FC+DF+2,1,2</t>
+          <t>SS+1+2</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Quick Uppercut Rush</t>
+          <t>Double Knuckle Swing</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Quick Uppercut Rush</t>
+          <t>Double Knuckle Swing</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>1 1 1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>-9 -2 -9</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>-9 -2 -9</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>-2 +10 +2</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>-2 +10 +2</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>-2 +10 +2</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>-2 +10 +2</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>15,10,15</t>
+          <t>35</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>35</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>15,10,15</t>
+          <t>35</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>mmm</t>
+          <t>h</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>mmm</t>
-        </is>
-      </c>
-      <c r="Y74" t="inlineStr">
-        <is>
-          <t>JGc RC</t>
-        </is>
-      </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>Juggles on the last hit if the first hit was a counter hit.</t>
+          <t>h</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>38964142-4e38-457c-9a6d-9ef0fcf12cd4</t>
+          <t>15c368e0-8f76-42a0-bbea-ef3cc510e19c</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>8efe400a-6435-45e4-92f5-b9e1d4fd9595</t>
+          <t>2f8a7e04-7a60-430d-bc0a-6a55ed0d3427</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="B75" t="inlineStr">
         <is>
-          <t>DF+2,1,2,1</t>
+          <t>1+2&lt;1+2</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>DF+2 ,1 ,2 ,1</t>
+          <t>1+2 &lt;1+2</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Hammer Uppercut Rush</t>
+          <t>Hammer Knuckle - Double Uppercut</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hammer Uppercut Rush</t>
+          <t>Hammer Knuckle - Double Uppercut</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>1 1 1 1</t>
+          <t>1 1</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>-11 -6 -9 -1</t>
+          <t>-15 -20</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>-11 -6 -9 -1</t>
+          <t>-15 -20</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>KD +5 +3 +10</t>
+          <t>KD KD</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>KD +5 +3 +10</t>
+          <t>KD KD</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>KD +5 +3 +10</t>
+          <t>KD KD</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>KD +5 +3 +10</t>
+          <t>KD KD</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>10,15,12,15</t>
+          <t>21,22</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>43</t>
         </is>
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>10,15,12,15</t>
+          <t>21,22</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>mmmm</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>mmmm</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>JG RC</t>
+          <t>JG</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>f62fd939-223c-47b4-982b-aecff23cfca4</t>
+          <t>54667fc1-c443-4001-a9d7-46c1d391bc4d</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>e85a400e-73a4-495b-917a-82244da3681f</t>
+          <t>36af744c-98c3-48c0-bea9-c96c61093c26</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="B76" t="inlineStr">
         <is>
-          <t>f,f+2</t>
+          <t>WS+1+2&lt;1+2</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>f,f+2</t>
+          <t>WS+1+2 &lt;1+2</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Atomic Hook</t>
+          <t>Double Uppercut - Hammer Knuckle</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Atomic Hook</t>
+          <t>Double Uppercut - Hammer Knuckle</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1 1</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-15 -16</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-15 -16</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>KD KD</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>KD KD</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>KD KD</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>KD KD</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>21,17</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>38</t>
         </is>
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>21,17</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>JG</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>e3ef4e95-cdea-4525-83df-74474e814b2a</t>
+          <t>14470b5f-e125-4262-857b-20fa6db24ee3</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>e14fe285-946c-414b-88e4-d7e2f3af2745</t>
+          <t>45985eea-a458-447f-9b9d-941ed088446a</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="B77" t="inlineStr">
         <is>
-          <t>2,1,2</t>
+          <t>f+1+2</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2 ,1 ,2</t>
+          <t>f+1+2</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Punch - Elbow - Uppercut</t>
+          <t>Arm Scissors</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Punch - Elbow - Uppercut</t>
+          <t>Arm Scissors</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>1 1 1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>0 0 -15</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>0 0 -15</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>+7 +2 KD</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>+7 +2 KD</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>+7 +2 KD</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>+7 +2 KD</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>12,15,20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>17</t>
         </is>
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>12,15,20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>m</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>m</t>
         </is>
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>JG</t>
-        </is>
-      </c>
-      <c r="AA77" t="inlineStr">
-        <is>
-          <t>TRUE</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>b51b9f18-a0d7-4234-b6c4-e0db8e729094</t>
+          <t>fab4def4-7c2d-4882-ac15-2c257a91fc81</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>06e4e99f-b024-4491-a080-43e24bdee8bc</t>
+          <t>f51b4cde-994c-422f-b3e6-3e932f7d87ff</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="B78" t="inlineStr">
         <is>
-          <t>DF,2</t>
+          <t>– 1+2</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>DF,2</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>FC+df+2</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>FC+df+2</t>
+          <t>f+1+2 ,1+2</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Short Hammer Rush</t>
+          <t>– Cross Cut Saw</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Short Hammer Rush</t>
+          <t>Arm Scissors – Cross Cut Saw</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>18</t>
+          <t>1 1</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>-13</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>-13</t>
+          <t>-10 -14</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>KD KD</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>KD KD</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>17,15</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>l</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="Y78" t="inlineStr">
@@ -7718,34 +7248,39 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>0e04bfed-33f9-495b-b9db-252a47602a7d</t>
+          <t>acab70ca-8813-48c6-907e-58ba82b57685</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>d79c3cf7-3a6f-4c0a-b31a-e35de47e6878</t>
+          <t>e7af4cd0-902b-4b89-9c43-ea9365bec42c</t>
+        </is>
+      </c>
+      <c r="AD78" t="inlineStr">
+        <is>
+          <t>fab4def4-7c2d-4882-ac15-2c257a91fc81</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="B79" t="inlineStr">
         <is>
-          <t>– d+1</t>
+          <t>– ~df+2</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>DF,2 ,d+1</t>
+          <t>f+1+2 ~df+2</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>– Low Punch</t>
+          <t>– Megaton Punch</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Short Hammer Rush – Low Punch</t>
+          <t>Arm Scissors – Megaton Punch</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -7755,62 +7290,62 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>-19</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>-13 -17</t>
+          <t>-10 -19</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>-2 -7</t>
+          <t>KD KD</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>-2 -7</t>
+          <t>KD KD</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>25</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>25</t>
         </is>
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>10,8</t>
+          <t>17,25</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>m</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
         <is>
-          <t>mL</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="Y79" t="inlineStr">
@@ -7820,94 +7355,99 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>82744639-21bd-464e-acb0-fb430a833b71</t>
+          <t>773af138-28f0-48ff-9b0e-97e83d2d8d3f</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>da44dd7b-4cdb-4823-a817-06318a68273c</t>
+          <t>b671f9fe-a460-4157-8300-00379e99322d</t>
         </is>
       </c>
       <c r="AD79" t="inlineStr">
         <is>
-          <t>0e04bfed-33f9-495b-b9db-252a47602a7d</t>
+          <t>fab4def4-7c2d-4882-ac15-2c257a91fc81</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="B80" t="inlineStr">
         <is>
-          <t>– df+1</t>
+          <t>d+1+2</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>DF,2 ,df+1</t>
+          <t>d+1+2</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>– Mid Punch</t>
+          <t>Bravo Knuckle</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Short Hammer Rush – Mid Punch</t>
+          <t>Bravo Knuckle</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>1 1</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>30</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-23</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>-13 -1</t>
+          <t>-23</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>+10</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>-2 +10</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>+10</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>-2 +10</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>45</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>45</t>
         </is>
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>10,15</t>
+          <t>45</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
@@ -7917,370 +7457,390 @@
       </c>
       <c r="V80" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>m</t>
         </is>
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>RC</t>
+          <t>JG GB</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>When tagging in Bryan Fury hit 2 to grab the opponent in mid air and do a Fisherman's Slam. Total damage is 21,21.</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>9cba188e-9985-4f96-83e4-7db5474781d2</t>
+          <t>f79bf7d8-dcd1-4a58-883f-38e113a7b9e1</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>51f0fb87-39b1-45cd-ab41-c081312a5d9b</t>
-        </is>
-      </c>
-      <c r="AD80" t="inlineStr">
-        <is>
-          <t>0e04bfed-33f9-495b-b9db-252a47602a7d</t>
+          <t>2ecc5ad9-b4ca-485a-884a-0301a91b3509</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="B81" t="inlineStr">
         <is>
-          <t>– f+1</t>
+          <t>FC+1+2</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>DF,2 ,f+1</t>
+          <t>FC+1+2</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>– High Punch</t>
+          <t>Cross Cut Saw</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Short Hammer Rush – High Punch</t>
+          <t>Cross Cut Saw</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>1 1</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>21</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>-19</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>-13 -17</t>
+          <t>-19</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>-2 -5</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>-2 -5</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>21</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>21</t>
         </is>
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>10,12</t>
+          <t>21</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>l</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
         <is>
-          <t>mh</t>
+          <t>l</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>RC</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>9dd1c03f-e1e1-4e41-b91a-88df8054ec5c</t>
+          <t>23e71f4e-0ab8-4ddc-89c1-4b2fe81234cc</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>529ea903-bd1d-4081-ab74-eb6b82eaab94</t>
-        </is>
-      </c>
-      <c r="AD81" t="inlineStr">
-        <is>
-          <t>0e04bfed-33f9-495b-b9db-252a47602a7d</t>
+          <t>52606470-ef56-4c68-a311-9fe12c9a5f23</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="B82" t="inlineStr">
         <is>
-          <t>b,db,d,DF+2</t>
+          <t>DF,2,1,2</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>b,db,d,DF+2</t>
+          <t>DF,2 ,1 ,2</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>FC+DF+2,1,2</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>FC+DF+2,1,2</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Megaton Punch</t>
+          <t>Quick Uppercut Rush</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Megaton Punch</t>
+          <t>Quick Uppercut Rush</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1 1 1</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>18</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>-9 -2 -9</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>-9 -2 -9</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-2 +10 +2</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-2 +10 +2</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-2 +10 +2</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-2 +10 +2</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>15,10,15</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>40</t>
         </is>
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>15,10,15</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>mmm</t>
         </is>
       </c>
       <c r="V82" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>mmm</t>
         </is>
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>RC</t>
+          <t>JGc RC</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>Juggles on the last hit if the first hit was a counter hit.</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>56b1623c-ef98-42a3-be49-2ebc46462a0f</t>
+          <t>38964142-4e38-457c-9a6d-9ef0fcf12cd4</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>e818b2a1-12e3-409b-8e48-4b059aaa76c0</t>
+          <t>8efe400a-6435-45e4-92f5-b9e1d4fd9595</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="B83" t="inlineStr">
         <is>
-          <t>f,f+3</t>
+          <t>DF+2,1,2,1</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>f,f+3</t>
+          <t>DF+2 ,1 ,2 ,1</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Granite Stomp</t>
+          <t>Hammer Uppercut Rush</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Granite Stomp</t>
+          <t>Hammer Uppercut Rush</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1 1 1 1</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>-11 -6 -9 -1</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>-11 -6 -9 -1</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>KD +5 +3 +10</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>KD +5 +3 +10</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>KD +5 +3 +10</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>KD +5 +3 +10</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>10,15,12,15</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>52</t>
         </is>
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>10,15,12,15</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>mmmm</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>mmmm</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>JG RC</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>ee6c0589-29fe-439a-8f69-242d8e6811f6</t>
+          <t>f62fd939-223c-47b4-982b-aecff23cfca4</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>879d1a1f-95b2-4081-aa4b-dc74da0c13c6</t>
+          <t>e85a400e-73a4-495b-917a-82244da3681f</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="B84" t="inlineStr">
         <is>
-          <t>f+3+4</t>
+          <t>f,f+2</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>f+3+4</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>FC+df+3+4</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>FC+df+3+4</t>
+          <t>f,f+2</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Giga Shoulder Ram</t>
+          <t>Atomic Hook</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Giga Shoulder Ram</t>
+          <t>Atomic Hook</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -8290,22 +7850,22 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -8330,166 +7890,181 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>h</t>
         </is>
       </c>
       <c r="V84" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>h</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>20d7633a-2326-4494-84f9-0a235f1c2fe8</t>
+          <t>e3ef4e95-cdea-4525-83df-74474e814b2a</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>b0da65f9-bf50-406e-8de8-7db02d0abb2c</t>
+          <t>e14fe285-946c-414b-88e4-d7e2f3af2745</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="B85" t="inlineStr">
         <is>
-          <t>DB+3,4,3,4,3,4</t>
+          <t>2,1,2</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>DB+3 ,4 ,3 ,4 ,3 ,4</t>
+          <t>2 ,1 ,2</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Cossack Kicks</t>
+          <t>Punch - Elbow - Uppercut</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cossack Kicks</t>
+          <t>Punch - Elbow - Uppercut</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>1 1 1 1 1 1</t>
+          <t>1 1 1</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>-20 -22 -20 -22 -20 -22</t>
+          <t>0 0 -15</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>-20 -22 -20 -22 -20 -22</t>
+          <t>0 0 -15</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>-9 -11 -9 -11 -9 -11</t>
+          <t>+7 +2 KD</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>-9 -11 -9 -11 -9 -11</t>
+          <t>+7 +2 KD</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>-9 -11 -9 -11 -9 -11</t>
+          <t>+7 +2 KD</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>-9 -11 -9 -11 -9 -11</t>
+          <t>+7 +2 KD</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>18,12,10,12,12,12</t>
+          <t>12,15,20</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>47</t>
         </is>
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>18,12,10,12,12,12</t>
+          <t>12,15,20</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>LLLLLL</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="V85" t="inlineStr">
         <is>
-          <t>LLLLLL</t>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>674f6841-5fbb-4b15-865f-9ab351c1a0f0</t>
+          <t>b51b9f18-a0d7-4234-b6c4-e0db8e729094</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>4c477a6b-86e6-43f8-911d-93481004b0b5</t>
+          <t>06e4e99f-b024-4491-a080-43e24bdee8bc</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="B86" t="inlineStr">
         <is>
-          <t>uf+3+4</t>
+          <t>DF,2</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>uf+3+4</t>
+          <t>DF,2</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>FC+df+2</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>FC+df+2</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Hip Press</t>
+          <t>Short Hammer Rush</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hip Press</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>(~B)Roll back; (~F)Roll forward</t>
+          <t>Short Hammer Rush</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -8499,799 +8074,965 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>18</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>-40</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>-40</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>-40</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>-40</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>10</t>
         </is>
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>10</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>m</t>
         </is>
       </c>
       <c r="V86" t="inlineStr">
         <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>If the Hip Press Misses the opponent, Jack-2 can chain into Sit Down extentions.</t>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>RC</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>3be14565-e783-4db3-9168-bf98e290f21d</t>
+          <t>0e04bfed-33f9-495b-b9db-252a47602a7d</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>ce4da910-2232-4be6-a896-136d900764e1</t>
+          <t>d79c3cf7-3a6f-4c0a-b31a-e35de47e6878</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="B87" t="inlineStr">
         <is>
-          <t>3+4</t>
+          <t>– d+1</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>3+4</t>
+          <t>DF,2 ,d+1</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Sit Down</t>
+          <t>– Low Punch</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Sit Down</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>(~B)Roll back; (~F)Roll forward; (~U)Hop up</t>
+          <t>Short Hammer Rush – Low Punch</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1 1</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>-17</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>-13 -17</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>-7</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>-2 -7</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>-7</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>-2 -7</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10,8</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>L</t>
         </is>
       </c>
       <c r="V87" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>mL</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>RC</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>3f1586e3-7d70-40ce-a201-943ab9917e0a</t>
+          <t>82744639-21bd-464e-acb0-fb430a833b71</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>8ff726df-3bc4-4645-98be-c2fad557ee7d</t>
+          <t>da44dd7b-4cdb-4823-a817-06318a68273c</t>
+        </is>
+      </c>
+      <c r="AD87" t="inlineStr">
+        <is>
+          <t>0e04bfed-33f9-495b-b9db-252a47602a7d</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="B88" t="inlineStr">
         <is>
-          <t>– ~3+4</t>
+          <t>– df+1</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>3+4 ~3+4</t>
+          <t>DF,2 ,df+1</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>– Hop Hip Press</t>
+          <t>– Mid Punch</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Sit Down – Hop Hip Press</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>(~B)Roll back; (~F)Roll forward</t>
+          <t>Short Hammer Rush – Mid Punch</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>0 1</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>62</t>
+          <t>1 1</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>18</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>-13 -1</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>-34</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>-34</t>
+          <t>-2 +10</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>-34</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>-34</t>
+          <t>-2 +10</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>15</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>15</t>
         </is>
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>-,35</t>
+          <t>10,15</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>m</t>
         </is>
       </c>
       <c r="V88" t="inlineStr">
         <is>
-          <t>-M</t>
-        </is>
-      </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>If the Hip Press Misses the opponent, Jack-2 can chain into Sit Down extentions.</t>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>RC</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>421087d9-77e4-4344-95d3-0ffee0325022</t>
+          <t>9cba188e-9985-4f96-83e4-7db5474781d2</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>1f37a24d-750f-4851-a2b5-a6b9a1b4ed26</t>
+          <t>51f0fb87-39b1-45cd-ab41-c081312a5d9b</t>
         </is>
       </c>
       <c r="AD88" t="inlineStr">
         <is>
-          <t>3f1586e3-7d70-40ce-a201-943ab9917e0a</t>
+          <t>0e04bfed-33f9-495b-b9db-252a47602a7d</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="B89" t="inlineStr">
         <is>
-          <t>– 1,2,1,2</t>
+          <t>– f+1</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>3+4 ,1 ,2 ,1 ,2</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>2,1,2,1</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>3+4,2,1,2,1</t>
+          <t>DF,2 ,f+1</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>– Sitting Punches</t>
+          <t>– High Punch</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Sit Down – Sitting Punches</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
+          <t>Short Hammer Rush – High Punch</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>1 1</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>-17</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>-13 -17</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>-2 -5</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>-2 -5</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>10,12</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>mh</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>9dd1c03f-e1e1-4e41-b91a-88df8054ec5c</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>529ea903-bd1d-4081-ab74-eb6b82eaab94</t>
+        </is>
+      </c>
+      <c r="AD89" t="inlineStr">
+        <is>
+          <t>0e04bfed-33f9-495b-b9db-252a47602a7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>b,db,d,DF+2</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>b,db,d,DF+2</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Megaton Punch</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Megaton Punch</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>-17</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>-17</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>RC</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>56b1623c-ef98-42a3-be49-2ebc46462a0f</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>e818b2a1-12e3-409b-8e48-4b059aaa76c0</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>f,f+3</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>f,f+3</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Granite Stomp</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Granite Stomp</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>+3</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>+3</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>ee6c0589-29fe-439a-8f69-242d8e6811f6</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>879d1a1f-95b2-4081-aa4b-dc74da0c13c6</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>f+3+4</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>f+3+4</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>FC+df+3+4</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>FC+df+3+4</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Giga Shoulder Ram</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Giga Shoulder Ram</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>-7</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>-7</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>20d7633a-2326-4494-84f9-0a235f1c2fe8</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>b0da65f9-bf50-406e-8de8-7db02d0abb2c</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>DB+3,4,3,4,3,4</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>DB+3 ,4 ,3 ,4 ,3 ,4</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Cossack Kicks</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Cossack Kicks</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>1 1 1 1 1 1</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>-20 -22 -20 -22 -20 -22</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>-20 -22 -20 -22 -20 -22</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>-9 -11 -9 -11 -9 -11</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>-9 -11 -9 -11 -9 -11</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>-9 -11 -9 -11 -9 -11</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>-9 -11 -9 -11 -9 -11</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>18,12,10,12,12,12</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>18,12,10,12,12,12</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>LLLLLL</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>LLLLLL</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>674f6841-5fbb-4b15-865f-9ab351c1a0f0</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>4c477a6b-86e6-43f8-911d-93481004b0b5</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>uf+3+4</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>uf+3+4</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Hip Press</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Hip Press</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
         <is>
           <t>(~B)Roll back; (~F)Roll forward</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>0 1 1 1 1</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>-45 -43 -45 -43</t>
-        </is>
-      </c>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>-45 -43 -45 -43</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr">
-        <is>
-          <t>-35 -32 -35 -32</t>
-        </is>
-      </c>
-      <c r="O89" t="inlineStr">
-        <is>
-          <t>-35 -32 -35 -32</t>
-        </is>
-      </c>
-      <c r="P89" t="inlineStr">
-        <is>
-          <t>-35 -32 -35 -32</t>
-        </is>
-      </c>
-      <c r="Q89" t="inlineStr">
-        <is>
-          <t>-35 -32 -35 -32</t>
-        </is>
-      </c>
-      <c r="R89" t="inlineStr">
-        <is>
-          <t>10,10,10,10</t>
-        </is>
-      </c>
-      <c r="S89" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="T89" t="inlineStr">
-        <is>
-          <t>-,10,10,10,10</t>
-        </is>
-      </c>
-      <c r="U89" t="inlineStr">
-        <is>
-          <t>llll</t>
-        </is>
-      </c>
-      <c r="V89" t="inlineStr">
-        <is>
-          <t>-llll</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>1e575213-1523-40b8-9492-0a92235d1799</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>71c8d35f-24b6-430d-abc5-2ff4c47a8f3b</t>
-        </is>
-      </c>
-      <c r="AD89" t="inlineStr">
-        <is>
-          <t>3f1586e3-7d70-40ce-a201-943ab9917e0a</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>KND</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>d+1+2</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>d+1+2</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>Spring Hammer - Sit Down</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>Spring Hammer - Sit Down</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
+      <c r="I94" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>+20</t>
-        </is>
-      </c>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>+20</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr">
-        <is>
-          <t>+14</t>
-        </is>
-      </c>
-      <c r="O90" t="inlineStr">
-        <is>
-          <t>+14</t>
-        </is>
-      </c>
-      <c r="P90" t="inlineStr">
-        <is>
-          <t>+14</t>
-        </is>
-      </c>
-      <c r="Q90" t="inlineStr">
-        <is>
-          <t>+14</t>
-        </is>
-      </c>
-      <c r="R90" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S90" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="T90" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="U90" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="V90" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>9ea7e1a3-859f-438a-b3fc-0ff0de0e315f</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>0066d9e6-44cc-4c22-b95a-1c01b1cb1dcb</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>KND</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>– 1,2,1,2</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>d+1+2 ,1 ,2 ,1 ,2</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>2,1,2,1</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>KND d+1+2,2,1,2,1</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>– Sitting Punches</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>Spring Hammer - Sit Down – Sitting Punches</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>(~B)Roll back; (~F)Roll forward</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>1 1 1 1 1</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>-45 -43 -45 -43</t>
-        </is>
-      </c>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>+20 -45 -43 -45 -43</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr">
-        <is>
-          <t>-35 -32 -35 -32</t>
-        </is>
-      </c>
-      <c r="O91" t="inlineStr">
-        <is>
-          <t>+14 -35 -32 -35 -32</t>
-        </is>
-      </c>
-      <c r="P91" t="inlineStr">
-        <is>
-          <t>-35 -32 -35 -32</t>
-        </is>
-      </c>
-      <c r="Q91" t="inlineStr">
-        <is>
-          <t>+14 -35 -32 -35 -32</t>
-        </is>
-      </c>
-      <c r="R91" t="inlineStr">
-        <is>
-          <t>10,10,10,10</t>
-        </is>
-      </c>
-      <c r="S91" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="T91" t="inlineStr">
-        <is>
-          <t>12,10,10,10,10</t>
-        </is>
-      </c>
-      <c r="U91" t="inlineStr">
-        <is>
-          <t>llll</t>
-        </is>
-      </c>
-      <c r="V91" t="inlineStr">
-        <is>
-          <t>mllll</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>eb0c424e-d4b0-438e-bfb7-164bbca1894a</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>01e88eb2-b793-4ba3-9d87-7f7b3ab33381</t>
-        </is>
-      </c>
-      <c r="AD91" t="inlineStr">
-        <is>
-          <t>9ea7e1a3-859f-438a-b3fc-0ff0de0e315f</t>
-        </is>
-      </c>
-    </row>
-    <row r="92"/>
-    <row r="93">
-      <c r="A93" s="1" t="inlineStr">
-        <is>
-          <t>Unblockable Arts</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="1" t="inlineStr">
-        <is>
-          <t>From Stance</t>
-        </is>
-      </c>
-      <c r="B94" s="1" t="inlineStr">
-        <is>
-          <t>Command</t>
-        </is>
-      </c>
-      <c r="C94" s="1" t="inlineStr">
-        <is>
-          <t>Command Full</t>
-        </is>
-      </c>
-      <c r="D94" s="1" t="inlineStr">
-        <is>
-          <t>Alt Commands</t>
-        </is>
-      </c>
-      <c r="E94" s="1" t="inlineStr">
-        <is>
-          <t>Alt Commands Full</t>
-        </is>
-      </c>
-      <c r="F94" s="1" t="inlineStr">
-        <is>
-          <t>Move Name</t>
-        </is>
-      </c>
-      <c r="G94" s="1" t="inlineStr">
-        <is>
-          <t>Move Name Full</t>
-        </is>
-      </c>
-      <c r="H94" s="1" t="inlineStr">
-        <is>
-          <t>To Stance</t>
-        </is>
-      </c>
-      <c r="I94" s="1" t="inlineStr">
-        <is>
-          <t>Hits Per Move</t>
-        </is>
-      </c>
-      <c r="J94" s="1" t="inlineStr">
-        <is>
-          <t>Speed</t>
-        </is>
-      </c>
-      <c r="K94" s="1" t="inlineStr">
-        <is>
-          <t>Speed Full</t>
-        </is>
-      </c>
-      <c r="L94" s="1" t="inlineStr">
-        <is>
-          <t>Block Adv</t>
-        </is>
-      </c>
-      <c r="M94" s="1" t="inlineStr">
-        <is>
-          <t>Block Adv Full</t>
-        </is>
-      </c>
-      <c r="N94" s="1" t="inlineStr">
-        <is>
-          <t>Hit Adv</t>
-        </is>
-      </c>
-      <c r="O94" s="1" t="inlineStr">
-        <is>
-          <t>Hit Adv Full</t>
-        </is>
-      </c>
-      <c r="P94" s="1" t="inlineStr">
-        <is>
-          <t>Counter Hit Adv</t>
-        </is>
-      </c>
-      <c r="Q94" s="1" t="inlineStr">
-        <is>
-          <t>Counter Hit Adv Full</t>
-        </is>
-      </c>
-      <c r="R94" s="1" t="inlineStr">
-        <is>
-          <t>Damage</t>
-        </is>
-      </c>
-      <c r="S94" s="1" t="inlineStr">
-        <is>
-          <t>Damage Sum</t>
-        </is>
-      </c>
-      <c r="T94" s="1" t="inlineStr">
-        <is>
-          <t>Damage Full</t>
-        </is>
-      </c>
-      <c r="U94" s="1" t="inlineStr">
-        <is>
-          <t>Hit Range</t>
-        </is>
-      </c>
-      <c r="V94" s="1" t="inlineStr">
-        <is>
-          <t>Hit Range Full</t>
-        </is>
-      </c>
-      <c r="W94" s="1" t="inlineStr">
-        <is>
-          <t>Throw Type</t>
-        </is>
-      </c>
-      <c r="X94" s="1" t="inlineStr">
-        <is>
-          <t>Throw Escape</t>
-        </is>
-      </c>
-      <c r="Y94" s="1" t="inlineStr">
-        <is>
-          <t>Properties</t>
-        </is>
-      </c>
-      <c r="Z94" s="1" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="AA94" s="1" t="inlineStr">
-        <is>
-          <t>Taggable</t>
-        </is>
-      </c>
-      <c r="AB94" s="1" t="inlineStr">
-        <is>
-          <t>UUID</t>
-        </is>
-      </c>
-      <c r="AC94" s="1" t="inlineStr">
-        <is>
-          <t>ML UUID</t>
-        </is>
-      </c>
-      <c r="AD94" s="1" t="inlineStr">
-        <is>
-          <t>Parent UUID</t>
-        </is>
-      </c>
-      <c r="AE94" s="1" t="inlineStr">
-        <is>
-          <t>Unmatched</t>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>-40</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>-40</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>-40</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>-40</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>If the Hip Press Misses the opponent, Jack-2 can chain into Sit Down extentions.</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>3be14565-e783-4db3-9168-bf98e290f21d</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>ce4da910-2232-4be6-a896-136d900764e1</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="B95" t="inlineStr">
         <is>
-          <t>hcf</t>
+          <t>3+4</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>hcf</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>b,b+1</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>b,b+1</t>
+          <t>3+4</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Gigaton Start Up</t>
+          <t>Sit Down</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Gigaton Start Up</t>
+          <t>Sit Down</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(~B)Roll back; (~F)Roll forward; (~U)Hop up</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R95" t="inlineStr">
@@ -9321,577 +9062,1016 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>d1938783-b653-4c21-91d7-5303ce4b61cb</t>
+          <t>3f1586e3-7d70-40ce-a201-943ab9917e0a</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>67a32d45-116c-42ad-88df-89b38e4ca9aa</t>
+          <t>8ff726df-3bc4-4645-98be-c2fad557ee7d</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="B96" t="inlineStr">
         <is>
-          <t>– b,db,d,df,f,uf,u,ub</t>
+          <t>– ~3+4</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>hcf,b,db,d,df,f,uf,u,ub</t>
+          <t>3+4 ~3+4</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>– Wind Up</t>
+          <t>– Hop Hip Press</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Gigaton Start Up – Wind Up</t>
+          <t>Sit Down – Hop Hip Press</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(~B)Roll back; (~F)Roll forward</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0 1</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>+3</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>+3</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>-34</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>-34</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>-34</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>-34</t>
         </is>
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>-,-</t>
+          <t>-,35</t>
         </is>
       </c>
       <c r="U96" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>M</t>
         </is>
       </c>
       <c r="V96" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>-M</t>
         </is>
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>Can be repeated up to 5 times.</t>
+          <t>If the Hip Press Misses the opponent, Jack-2 can chain into Sit Down extentions.</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>1f65d946-be2a-4bb4-9a27-18e4ad27b7a8</t>
+          <t>421087d9-77e4-4344-95d3-0ffee0325022</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>99aa8796-5bbe-4d4a-8523-9278daf2c772</t>
+          <t>1f37a24d-750f-4851-a2b5-a6b9a1b4ed26</t>
         </is>
       </c>
       <c r="AD96" t="inlineStr">
         <is>
-          <t>d1938783-b653-4c21-91d7-5303ce4b61cb</t>
+          <t>3f1586e3-7d70-40ce-a201-943ab9917e0a</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="B97" t="inlineStr">
         <is>
-          <t>–– 1</t>
+          <t>– 1,2,1,2</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>hcf,b,db,d,df,f,uf,u,ub,1</t>
+          <t>3+4 ,1 ,2 ,1 ,2</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>2,1,2,1</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>3+4,2,1,2,1</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>–– Gigaton Punch</t>
+          <t>– Sitting Punches</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Gigaton Start Up – Wind Up – Gigaton Punch</t>
+          <t>Sit Down – Sitting Punches</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(~B)Roll back; (~F)Roll forward</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
+          <t>0 1 1 1 1</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>-45 -43 -45 -43</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>-45 -43 -45 -43</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>-35 -32 -35 -32</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>-35 -32 -35 -32</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>-35 -32 -35 -32</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>-35 -32 -35 -32</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>10,10,10,10</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>-,10,10,10,10</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>llll</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>-llll</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>1e575213-1523-40b8-9492-0a92235d1799</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>71c8d35f-24b6-430d-abc5-2ff4c47a8f3b</t>
+        </is>
+      </c>
+      <c r="AD97" t="inlineStr">
+        <is>
+          <t>3f1586e3-7d70-40ce-a201-943ab9917e0a</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>KND</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>d+1+2</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>d+1+2</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Spring Hammer - Sit Down</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Spring Hammer - Sit Down</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="L97" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="O97" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="P97" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="Q97" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="R97" t="inlineStr">
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>+20</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>+20</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>+14</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>+14</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>+14</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>+14</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>9ea7e1a3-859f-438a-b3fc-0ff0de0e315f</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>0066d9e6-44cc-4c22-b95a-1c01b1cb1dcb</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>KND</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>– 1,2,1,2</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>d+1+2 ,1 ,2 ,1 ,2</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>2,1,2,1</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>KND d+1+2,2,1,2,1</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>– Sitting Punches</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Spring Hammer - Sit Down – Sitting Punches</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(~B)Roll back; (~F)Roll forward</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>1 1 1 1 1</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>-45 -43 -45 -43</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>+20 -45 -43 -45 -43</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>-35 -32 -35 -32</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>+14 -35 -32 -35 -32</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>-35 -32 -35 -32</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>+14 -35 -32 -35 -32</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>10,10,10,10</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="S97" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="T97" t="inlineStr">
-        <is>
-          <t>-,-,40</t>
-        </is>
-      </c>
-      <c r="U97" t="inlineStr">
-        <is>
-          <t>!</t>
-        </is>
-      </c>
-      <c r="V97" t="inlineStr">
-        <is>
-          <t>--!</t>
-        </is>
-      </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>Damage increases to 60, 80 and 199 with each extra Wind Up. Becomes Unblockable after 2 Wind Ups.</t>
-        </is>
-      </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>5effdb03-d23f-4671-8daa-b173c35d0ee4</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>8ae507ae-80ca-4f99-8564-71283564636c</t>
-        </is>
-      </c>
-      <c r="AD97" t="inlineStr">
-        <is>
-          <t>1f65d946-be2a-4bb4-9a27-18e4ad27b7a8</t>
-        </is>
-      </c>
-    </row>
-    <row r="98"/>
-    <row r="99">
-      <c r="A99" s="1" t="inlineStr">
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>12,10,10,10,10</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>llll</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>mllll</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>eb0c424e-d4b0-438e-bfb7-164bbca1894a</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>01e88eb2-b793-4ba3-9d87-7f7b3ab33381</t>
+        </is>
+      </c>
+      <c r="AD99" t="inlineStr">
+        <is>
+          <t>9ea7e1a3-859f-438a-b3fc-0ff0de0e315f</t>
+        </is>
+      </c>
+    </row>
+    <row r="100"/>
+    <row r="101">
+      <c r="A101" s="1" t="inlineStr">
+        <is>
+          <t>Unblockable Arts</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="inlineStr">
+        <is>
+          <t>From Stance</t>
+        </is>
+      </c>
+      <c r="B102" s="1" t="inlineStr">
+        <is>
+          <t>Command</t>
+        </is>
+      </c>
+      <c r="C102" s="1" t="inlineStr">
+        <is>
+          <t>Command Full</t>
+        </is>
+      </c>
+      <c r="D102" s="1" t="inlineStr">
+        <is>
+          <t>Alt Commands</t>
+        </is>
+      </c>
+      <c r="E102" s="1" t="inlineStr">
+        <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="F102" s="1" t="inlineStr">
+        <is>
+          <t>Move Name</t>
+        </is>
+      </c>
+      <c r="G102" s="1" t="inlineStr">
+        <is>
+          <t>Move Name Full</t>
+        </is>
+      </c>
+      <c r="H102" s="1" t="inlineStr">
+        <is>
+          <t>To Stance</t>
+        </is>
+      </c>
+      <c r="I102" s="1" t="inlineStr">
+        <is>
+          <t>Hits Per Move</t>
+        </is>
+      </c>
+      <c r="J102" s="1" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="K102" s="1" t="inlineStr">
+        <is>
+          <t>Speed Full</t>
+        </is>
+      </c>
+      <c r="L102" s="1" t="inlineStr">
+        <is>
+          <t>Block Adv</t>
+        </is>
+      </c>
+      <c r="M102" s="1" t="inlineStr">
+        <is>
+          <t>Block Adv Full</t>
+        </is>
+      </c>
+      <c r="N102" s="1" t="inlineStr">
+        <is>
+          <t>Hit Adv</t>
+        </is>
+      </c>
+      <c r="O102" s="1" t="inlineStr">
+        <is>
+          <t>Hit Adv Full</t>
+        </is>
+      </c>
+      <c r="P102" s="1" t="inlineStr">
+        <is>
+          <t>Counter Hit Adv</t>
+        </is>
+      </c>
+      <c r="Q102" s="1" t="inlineStr">
+        <is>
+          <t>Counter Hit Adv Full</t>
+        </is>
+      </c>
+      <c r="R102" s="1" t="inlineStr">
+        <is>
+          <t>Damage</t>
+        </is>
+      </c>
+      <c r="S102" s="1" t="inlineStr">
+        <is>
+          <t>Damage Sum</t>
+        </is>
+      </c>
+      <c r="T102" s="1" t="inlineStr">
+        <is>
+          <t>Damage Full</t>
+        </is>
+      </c>
+      <c r="U102" s="1" t="inlineStr">
+        <is>
+          <t>Hit Range</t>
+        </is>
+      </c>
+      <c r="V102" s="1" t="inlineStr">
+        <is>
+          <t>Hit Range Full</t>
+        </is>
+      </c>
+      <c r="W102" s="1" t="inlineStr">
+        <is>
+          <t>Throw Type</t>
+        </is>
+      </c>
+      <c r="X102" s="1" t="inlineStr">
+        <is>
+          <t>Throw Escape</t>
+        </is>
+      </c>
+      <c r="Y102" s="1" t="inlineStr">
+        <is>
+          <t>Properties</t>
+        </is>
+      </c>
+      <c r="Z102" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="AA102" s="1" t="inlineStr">
+        <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="AB102" s="1" t="inlineStr">
+        <is>
+          <t>UUID</t>
+        </is>
+      </c>
+      <c r="AC102" s="1" t="inlineStr">
+        <is>
+          <t>ML UUID</t>
+        </is>
+      </c>
+      <c r="AD102" s="1" t="inlineStr">
+        <is>
+          <t>Parent UUID</t>
+        </is>
+      </c>
+      <c r="AE102" s="1" t="inlineStr">
+        <is>
+          <t>Unmatched</t>
+        </is>
+      </c>
+    </row>
+    <row r="103"/>
+    <row r="104">
+      <c r="A104" s="1" t="inlineStr">
         <is>
           <t>String Hit Arts</t>
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="1" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="1" t="inlineStr">
         <is>
           <t>From Stance</t>
         </is>
       </c>
-      <c r="B100" s="1" t="inlineStr">
+      <c r="B105" s="1" t="inlineStr">
         <is>
           <t>Command</t>
         </is>
       </c>
-      <c r="C100" s="1" t="inlineStr">
+      <c r="C105" s="1" t="inlineStr">
         <is>
           <t>Command Full</t>
         </is>
       </c>
-      <c r="D100" s="1" t="inlineStr">
+      <c r="D105" s="1" t="inlineStr">
         <is>
           <t>Alt Commands</t>
         </is>
       </c>
-      <c r="E100" s="1" t="inlineStr">
+      <c r="E105" s="1" t="inlineStr">
         <is>
           <t>Alt Commands Full</t>
         </is>
       </c>
-      <c r="F100" s="1" t="inlineStr">
+      <c r="F105" s="1" t="inlineStr">
         <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="G100" s="1" t="inlineStr">
+      <c r="G105" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="H100" s="1" t="inlineStr">
+      <c r="H105" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="I100" s="1" t="inlineStr">
+      <c r="I105" s="1" t="inlineStr">
         <is>
           <t>Hits Per Move</t>
         </is>
       </c>
-      <c r="J100" s="1" t="inlineStr">
+      <c r="J105" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="K100" s="1" t="inlineStr">
+      <c r="K105" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="L100" s="1" t="inlineStr">
+      <c r="L105" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="M100" s="1" t="inlineStr">
+      <c r="M105" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="N100" s="1" t="inlineStr">
+      <c r="N105" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="O100" s="1" t="inlineStr">
+      <c r="O105" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="P100" s="1" t="inlineStr">
+      <c r="P105" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="Q100" s="1" t="inlineStr">
+      <c r="Q105" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="R100" s="1" t="inlineStr">
+      <c r="R105" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="S100" s="1" t="inlineStr">
+      <c r="S105" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="T100" s="1" t="inlineStr">
+      <c r="T105" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="U100" s="1" t="inlineStr">
+      <c r="U105" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="V100" s="1" t="inlineStr">
+      <c r="V105" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="W100" s="1" t="inlineStr">
+      <c r="W105" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="X100" s="1" t="inlineStr">
+      <c r="X105" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="Y100" s="1" t="inlineStr">
+      <c r="Y105" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="Z100" s="1" t="inlineStr">
+      <c r="Z105" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="AA100" s="1" t="inlineStr">
+      <c r="AA105" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="AB100" s="1" t="inlineStr">
+      <c r="AB105" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="AC100" s="1" t="inlineStr">
+      <c r="AC105" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AD100" s="1" t="inlineStr">
+      <c r="AD105" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AE100" s="1" t="inlineStr">
+      <c r="AE105" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="B101" t="inlineStr">
+    <row r="106">
+      <c r="B106" t="inlineStr">
         <is>
           <t>D+2,1,1,1,2,1,2,1,1+2,1+2</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
+      <c r="C106" t="inlineStr">
         <is>
           <t>D+2 ,1 ,1 ,1 ,2 ,1 ,2 ,1 ,1+2 ,1+2</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr">
+      <c r="I106" t="inlineStr">
         <is>
           <t>1 1 1 1 1 1 1 1 1 1</t>
         </is>
       </c>
-      <c r="R101" t="inlineStr">
+      <c r="R106" t="inlineStr">
         <is>
           <t>10,6,5,7,7,6,6,8,21,25</t>
         </is>
       </c>
-      <c r="S101" t="inlineStr">
+      <c r="S106" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="T101" t="inlineStr">
+      <c r="T106" t="inlineStr">
         <is>
           <t>10,6,5,7,7,6,6,8,21,25</t>
         </is>
       </c>
-      <c r="U101" t="inlineStr">
+      <c r="U106" t="inlineStr">
         <is>
           <t>sLLmmmmmmm</t>
         </is>
       </c>
-      <c r="V101" t="inlineStr">
+      <c r="V106" t="inlineStr">
         <is>
           <t>sLLmmmmmmm</t>
         </is>
       </c>
-      <c r="AB101" t="inlineStr">
+      <c r="AB106" t="inlineStr">
         <is>
           <t>cedd2a7b-61d7-42fe-9349-42a2b1503d3f</t>
         </is>
       </c>
-      <c r="AC101" t="inlineStr">
+      <c r="AC106" t="inlineStr">
         <is>
           <t>cedd2a7b-61d7-42fe-9349-42a2b1503d3f</t>
         </is>
       </c>
-      <c r="AE101" t="inlineStr">
+      <c r="AE106" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="B102" t="inlineStr">
+    <row r="107">
+      <c r="B107" t="inlineStr">
         <is>
           <t>D+2,1,1,1,2,1,2,1,d+1+2,1+2</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr">
+      <c r="C107" t="inlineStr">
         <is>
           <t>D+2 ,1 ,1 ,1 ,2 ,1 ,2 ,1 ,d+1+2 ,1+2</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr">
+      <c r="I107" t="inlineStr">
         <is>
           <t>1 1 1 1 1 1 1 1 1 1</t>
         </is>
       </c>
-      <c r="R102" t="inlineStr">
+      <c r="R107" t="inlineStr">
         <is>
           <t>10,6,5,7,7,6,6,8,12,35</t>
         </is>
       </c>
-      <c r="S102" t="inlineStr">
+      <c r="S107" t="inlineStr">
         <is>
           <t>102</t>
         </is>
       </c>
-      <c r="T102" t="inlineStr">
+      <c r="T107" t="inlineStr">
         <is>
           <t>10,6,5,7,7,6,6,8,12,35</t>
         </is>
       </c>
-      <c r="U102" t="inlineStr">
+      <c r="U107" t="inlineStr">
         <is>
           <t>sLLmmmmmlm</t>
         </is>
       </c>
-      <c r="V102" t="inlineStr">
+      <c r="V107" t="inlineStr">
         <is>
           <t>sLLmmmmmlm</t>
         </is>
       </c>
-      <c r="AB102" t="inlineStr">
+      <c r="AB107" t="inlineStr">
         <is>
           <t>46414757-6bbc-43ff-bcce-43bb3e815b75</t>
         </is>
       </c>
-      <c r="AC102" t="inlineStr">
+      <c r="AC107" t="inlineStr">
         <is>
           <t>46414757-6bbc-43ff-bcce-43bb3e815b75</t>
         </is>
       </c>
-      <c r="AE102" t="inlineStr">
+      <c r="AE107" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="B103" t="inlineStr">
+    <row r="108">
+      <c r="B108" t="inlineStr">
         <is>
           <t>uf+1,1,4,3,4,1,2,1,1+2,1+2</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
+      <c r="C108" t="inlineStr">
         <is>
           <t>uf+1 ,1 ,4 ,3 ,4 ,1 ,2 ,1 ,1+2 ,1+2</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr">
+      <c r="I108" t="inlineStr">
         <is>
           <t>1 1 1 1 1 1 1 1 1 1</t>
         </is>
       </c>
-      <c r="R103" t="inlineStr">
+      <c r="R108" t="inlineStr">
         <is>
           <t>15,8,5,5,5,8,6,8,21,25</t>
         </is>
       </c>
-      <c r="S103" t="inlineStr">
+      <c r="S108" t="inlineStr">
         <is>
           <t>106</t>
         </is>
       </c>
-      <c r="T103" t="inlineStr">
+      <c r="T108" t="inlineStr">
         <is>
           <t>15,8,5,5,5,8,6,8,21,25</t>
         </is>
       </c>
-      <c r="U103" t="inlineStr">
+      <c r="U108" t="inlineStr">
         <is>
           <t>hmLLLmmmmm</t>
         </is>
       </c>
-      <c r="V103" t="inlineStr">
+      <c r="V108" t="inlineStr">
         <is>
           <t>hmLLLmmmmm</t>
         </is>
       </c>
-      <c r="AB103" t="inlineStr">
+      <c r="AB108" t="inlineStr">
         <is>
           <t>66ed2d10-6ef0-489d-ad01-ab4680052d18</t>
         </is>
       </c>
-      <c r="AC103" t="inlineStr">
+      <c r="AC108" t="inlineStr">
         <is>
           <t>66ed2d10-6ef0-489d-ad01-ab4680052d18</t>
         </is>
       </c>
-      <c r="AE103" t="inlineStr">
+      <c r="AE108" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="B104" t="inlineStr">
+    <row r="109">
+      <c r="B109" t="inlineStr">
         <is>
           <t>uf+1,1,4,3,4,12,1,d+1+2,1+2</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
+      <c r="C109" t="inlineStr">
         <is>
           <t>uf+1 ,1 ,4 ,3 ,4 ,12 ,1 ,d+1+2 ,1+2</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr">
+      <c r="I109" t="inlineStr">
         <is>
           <t>1 1 1 1 1 1 1 1 1</t>
         </is>
       </c>
-      <c r="R104" t="inlineStr">
+      <c r="R109" t="inlineStr">
         <is>
           <t>15,8,5,5,5,8,6,8,12,35</t>
         </is>
       </c>
-      <c r="S104" t="inlineStr">
+      <c r="S109" t="inlineStr">
         <is>
           <t>107</t>
         </is>
       </c>
-      <c r="T104" t="inlineStr">
+      <c r="T109" t="inlineStr">
         <is>
           <t>15,8,5,5,5,8,6,8,12,35</t>
         </is>
       </c>
-      <c r="U104" t="inlineStr">
+      <c r="U109" t="inlineStr">
         <is>
           <t>hmLLLmmmlm</t>
         </is>
       </c>
-      <c r="V104" t="inlineStr">
+      <c r="V109" t="inlineStr">
         <is>
           <t>hmLLLmmmlm</t>
         </is>
       </c>
-      <c r="AB104" t="inlineStr">
+      <c r="AB109" t="inlineStr">
         <is>
           <t>bfdf582e-6190-406a-b25c-eee25e104050</t>
         </is>
       </c>
-      <c r="AC104" t="inlineStr">
+      <c r="AC109" t="inlineStr">
         <is>
           <t>bfdf582e-6190-406a-b25c-eee25e104050</t>
         </is>
       </c>
-      <c r="AE104" t="inlineStr">
+      <c r="AE109" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
